--- a/data/helios_jobs_two_tabs.xlsx
+++ b/data/helios_jobs_two_tabs.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1243,12 +1243,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tech Economy</t>
+          <t>Flipkart</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Project Leader- Vector(Generalist)</t>
+          <t>Senior Staff Data Scientist</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/project-leader-vector-generalist-at-tech-economy-4417891327?position=5&amp;pageNum=0&amp;refId=QRvOtEJIeK0N0cB1zXedJg%3D%3D&amp;trackingId=GAOfpWdHnwAEKUB79tZu9Q%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/senior-staff-data-scientist-at-flipkart-4452388051?position=3&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=rSqFHtZXKahnxoqv4AFpYg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Senior Staff Data Scientist</t>
+          <t>Senior Architect - AI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/senior-staff-data-scientist-at-flipkart-4452388051?position=3&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=rSqFHtZXKahnxoqv4AFpYg%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/senior-architect-ai-at-flipkart-4443122009?position=4&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=ovjPBLn%2BAlD8pRIcp0fwuA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Senior Architect - AI</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1362,34 +1362,34 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/senior-architect-ai-at-flipkart-4443122009?position=4&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=ovjPBLn%2BAlD8pRIcp0fwuA%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/engineering-manager-at-flipkart-4446769850?position=5&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=7YVL2gAr1lRMrm6eqLq3Ug%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Flipkart</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Security and Loss Prevention Specialist, INTL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India</t>
+          <t>Janakpuri, Delhi, India</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1404,34 +1404,34 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/engineering-manager-at-flipkart-4446769850?position=5&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=7YVL2gAr1lRMrm6eqLq3Ug%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/security-and-loss-prevention-specialist-intl-at-amazon-4443046086?position=6&amp;pageNum=0&amp;refId=FQkQ8esI8YSTd58C7h5Q8A%3D%3D&amp;trackingId=E2jH%2F48ZMsB6qhuK9MW39A%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Security and Loss Prevention Specialist, INTL</t>
+          <t>Principal Architect</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Janakpuri, Delhi, India</t>
+          <t>Noida, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/security-and-loss-prevention-specialist-intl-at-amazon-4443046086?position=6&amp;pageNum=0&amp;refId=FQkQ8esI8YSTd58C7h5Q8A%3D%3D&amp;trackingId=E2jH%2F48ZMsB6qhuK9MW39A%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/principal-architect-at-microsoft-4419194854?position=1&amp;pageNum=0&amp;refId=j%2FK6Hlb%2F%2BicTmfvOYmOPcQ%3D%3D&amp;trackingId=LCXLnKPkOFcIv6fDvfVe%2Bg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Principal Architect</t>
+          <t>Principal Firmware Engineer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/principal-architect-at-microsoft-4419194854?position=1&amp;pageNum=0&amp;refId=j%2FK6Hlb%2F%2BicTmfvOYmOPcQ%3D%3D&amp;trackingId=LCXLnKPkOFcIv6fDvfVe%2Bg%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/principal-firmware-engineer-at-microsoft-4442471104?position=3&amp;pageNum=0&amp;refId=j%2FK6Hlb%2F%2BicTmfvOYmOPcQ%3D%3D&amp;trackingId=TFmGb1QUMtvcIPMtSHAYKQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1500,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Principal Firmware Engineer</t>
+          <t>Solution Area Specialists - Biz Apps</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh, India</t>
+          <t>Gurgaon, Haryana, India</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1530,29 +1530,29 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/principal-firmware-engineer-at-microsoft-4442471104?position=3&amp;pageNum=0&amp;refId=j%2FK6Hlb%2F%2BicTmfvOYmOPcQ%3D%3D&amp;trackingId=TFmGb1QUMtvcIPMtSHAYKQ%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/solution-area-specialists-biz-apps-at-microsoft-4436327516?position=6&amp;pageNum=0&amp;refId=j%2FK6Hlb%2F%2BicTmfvOYmOPcQ%3D%3D&amp;trackingId=V7ZCVj6PpymR6HT2Zfevvw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Google Operations Center</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Solution Area Specialists - Biz Apps</t>
+          <t>Process Excellence Senior Specialist</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1572,34 +1572,34 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/solution-area-specialists-biz-apps-at-microsoft-4436327516?position=6&amp;pageNum=0&amp;refId=j%2FK6Hlb%2F%2BicTmfvOYmOPcQ%3D%3D&amp;trackingId=V7ZCVj6PpymR6HT2Zfevvw%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/process-excellence-senior-specialist-at-google-operations-center-4374370308?position=4&amp;pageNum=0&amp;refId=q2iENRSjQZHdUesa6IkfUA%3D%3D&amp;trackingId=Kk%2FYzZnQ4cPKRbuVAyULBg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Google Operations Center</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Process Excellence Senior Specialist</t>
+          <t>Strategic Negotiator, Google Global Networking</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gurgaon, Haryana, India</t>
+          <t>Gurugram, Haryana, India</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/process-excellence-senior-specialist-at-google-operations-center-4374370308?position=4&amp;pageNum=0&amp;refId=q2iENRSjQZHdUesa6IkfUA%3D%3D&amp;trackingId=Kk%2FYzZnQ4cPKRbuVAyULBg%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/strategic-negotiator-google-global-networking-at-google-4451187494?position=5&amp;pageNum=0&amp;refId=q2iENRSjQZHdUesa6IkfUA%3D%3D&amp;trackingId=Ppmb%2BVuOpYYfaYnn%2BSjQuQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Strategic Negotiator, Google Global Networking</t>
+          <t>Product Support Consultant</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1656,19 +1656,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/strategic-negotiator-google-global-networking-at-google-4451187494?position=5&amp;pageNum=0&amp;refId=q2iENRSjQZHdUesa6IkfUA%3D%3D&amp;trackingId=Ppmb%2BVuOpYYfaYnn%2BSjQuQ%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/product-support-consultant-at-google-4437575226?position=6&amp;pageNum=0&amp;refId=q2iENRSjQZHdUesa6IkfUA%3D%3D&amp;trackingId=vzNVZ3dU9YLJtvjmbntk0w%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>MiM-Essay</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Product Support Consultant</t>
+          <t>Software Developer in Delhi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana, India</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1698,19 +1698,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/product-support-consultant-at-google-4437575226?position=6&amp;pageNum=0&amp;refId=q2iENRSjQZHdUesa6IkfUA%3D%3D&amp;trackingId=vzNVZ3dU9YLJtvjmbntk0w%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/software-developer-in-delhi-at-mim-essay-4445269379?position=3&amp;pageNum=0&amp;refId=NA1Rue%2FX8rQTNSd9nLv4yA%3D%3D&amp;trackingId=BbJtX6sQTbEZOwcf5JHpfQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MiM-Essay</t>
+          <t>House Technologies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Software Developer in Delhi</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>Rohini, Delhi, India</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1740,19 +1740,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-developer-in-delhi-at-mim-essay-4445269379?position=3&amp;pageNum=0&amp;refId=NA1Rue%2FX8rQTNSd9nLv4yA%3D%3D&amp;trackingId=BbJtX6sQTbEZOwcf5JHpfQ%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-at-house-technologies-4449966064?position=5&amp;pageNum=0&amp;refId=NA1Rue%2FX8rQTNSd9nLv4yA%3D%3D&amp;trackingId=hV87psvFLhcRuNid8XW6ug%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>House Technologies</t>
+          <t>Accenture in India</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Custom Software Engineer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rohini, Delhi, India</t>
+          <t>Gurugram, Haryana, India</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1782,19 +1782,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-engineer-at-house-technologies-4449966064?position=5&amp;pageNum=0&amp;refId=NA1Rue%2FX8rQTNSd9nLv4yA%3D%3D&amp;trackingId=hV87psvFLhcRuNid8XW6ug%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4448371975?position=1&amp;pageNum=0&amp;refId=Mg1TwPxgYEpEKoCJwbRoJw%3D%3D&amp;trackingId=QIt1DcRf5E5A9uU6Db%2BO6w%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Accenture in India</t>
+          <t>Scoutit India</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Custom Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1824,14 +1824,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4448371975?position=1&amp;pageNum=0&amp;refId=Mg1TwPxgYEpEKoCJwbRoJw%3D%3D&amp;trackingId=QIt1DcRf5E5A9uU6Db%2BO6w%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-at-scoutit-india-4453969708?position=3&amp;pageNum=0&amp;refId=Mg1TwPxgYEpEKoCJwbRoJw%3D%3D&amp;trackingId=Plfl03dB3YhlcIzowSD9rg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Scoutit India</t>
+          <t>Policybazaar.com</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1866,19 +1866,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-engineer-at-scoutit-india-4453969708?position=3&amp;pageNum=0&amp;refId=Mg1TwPxgYEpEKoCJwbRoJw%3D%3D&amp;trackingId=Plfl03dB3YhlcIzowSD9rg%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-at-policybazaar-com-4442808303?position=4&amp;pageNum=0&amp;refId=Mg1TwPxgYEpEKoCJwbRoJw%3D%3D&amp;trackingId=i41ZCTAJVqovgHG5%2BkL45A%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Policybazaar.com</t>
+          <t>Innovative Application Consultants</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Dynamics NAV | Business Central Functional Consultant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana, India</t>
+          <t>Nehru Place, Delhi, India</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1908,19 +1908,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-engineer-at-policybazaar-com-4442808303?position=4&amp;pageNum=0&amp;refId=Mg1TwPxgYEpEKoCJwbRoJw%3D%3D&amp;trackingId=i41ZCTAJVqovgHG5%2BkL45A%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/dynamics-nav-business-central-functional-consultant-at-innovative-application-consultants-4443321838?position=3&amp;pageNum=0&amp;refId=gBxjMCrCKahf%2Bpl8Fcnw2Q%3D%3D&amp;trackingId=epiYNuSQwrslfB6J%2BWIOGQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Innovative Application Consultants</t>
+          <t>Accenture in India</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dynamics NAV | Business Central Functional Consultant</t>
+          <t>Custom Software Engineer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nehru Place, Delhi, India</t>
+          <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1950,19 +1950,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/dynamics-nav-business-central-functional-consultant-at-innovative-application-consultants-4443321838?position=3&amp;pageNum=0&amp;refId=gBxjMCrCKahf%2Bpl8Fcnw2Q%3D%3D&amp;trackingId=epiYNuSQwrslfB6J%2BWIOGQ%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4454802373?position=1&amp;pageNum=0&amp;refId=EXawlZGc3gIwEXL63BgzfA%3D%3D&amp;trackingId=cECqLWsTpc6jRRsq%2B1JdIA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Accenture in India</t>
+          <t>Honeywell Technologies</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Custom Software Engineer</t>
+          <t>Software Engr II</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1992,19 +1992,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4454802373?position=1&amp;pageNum=0&amp;refId=EXawlZGc3gIwEXL63BgzfA%3D%3D&amp;trackingId=cECqLWsTpc6jRRsq%2B1JdIA%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/software-engr-ii-at-honeywell-technologies-4452434812?position=2&amp;pageNum=0&amp;refId=EXawlZGc3gIwEXL63BgzfA%3D%3D&amp;trackingId=rKtISlXAPI%2BYXRJXgE6w9A%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Honeywell Technologies</t>
+          <t>CBX1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Software Engr II</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2034,19 +2034,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-engr-ii-at-honeywell-technologies-4452434812?position=2&amp;pageNum=0&amp;refId=EXawlZGc3gIwEXL63BgzfA%3D%3D&amp;trackingId=rKtISlXAPI%2BYXRJXgE6w9A%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/software-developer-at-cbx1-4137534021?position=5&amp;pageNum=0&amp;refId=EXawlZGc3gIwEXL63BgzfA%3D%3D&amp;trackingId=%2FXoXwF6l17NztXI%2FNHhobQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CBX1</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Account Executive, Enterprise (Bengaluru, India)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-developer-at-cbx1-4137534021?position=5&amp;pageNum=0&amp;refId=EXawlZGc3gIwEXL63BgzfA%3D%3D&amp;trackingId=%2FXoXwF6l17NztXI%2FNHhobQ%3D%3D</t>
+          <t>https://boards.greenhouse.io/figma/jobs/5579204004?gh_jid=5579204004</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Account Executive, Enterprise (Bengaluru, India)</t>
+          <t xml:space="preserve">Account Executive </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Bengaluru, India; Mumbai, India</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2118,34 +2118,34 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5579204004?gh_jid=5579204004</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=6918763002</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Tech Economy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Account Executive </t>
+          <t>Project Leader (Commercial Acceleration) - Performance Improvement CoE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bengaluru, India; Mumbai, India</t>
+          <t>Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=6918763002</t>
+          <t>https://in.linkedin.com/jobs/view/project-leader-commercial-acceleration-performance-improvement-coe-at-tech-economy-4442649753?position=3&amp;pageNum=0&amp;refId=QRvOtEJIeK0N0cB1zXedJg%3D%3D&amp;trackingId=TsnBukj%2FBB6cmTahN8xMFw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Project Leader (Commercial Acceleration) - Performance Improvement CoE</t>
+          <t>Project Leader- Vector (Commercial CD)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2202,34 +2202,34 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/project-leader-commercial-acceleration-performance-improvement-coe-at-tech-economy-4442649753?position=3&amp;pageNum=0&amp;refId=QRvOtEJIeK0N0cB1zXedJg%3D%3D&amp;trackingId=TsnBukj%2FBB6cmTahN8xMFw%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/project-leader-vector-commercial-cd-at-tech-economy-4438328133?position=6&amp;pageNum=0&amp;refId=QRvOtEJIeK0N0cB1zXedJg%3D%3D&amp;trackingId=ePaAflysT2uCP1DC8WLepQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tech Economy</t>
+          <t>Flipkart</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Project Leader- Vector (Commercial CD)</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2244,19 +2244,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/project-leader-vector-commercial-cd-at-tech-economy-4438328133?position=6&amp;pageNum=0&amp;refId=QRvOtEJIeK0N0cB1zXedJg%3D%3D&amp;trackingId=ePaAflysT2uCP1DC8WLepQ%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/architect-at-flipkart-4442073191?position=1&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=UuVkxtYavjwIEq4Y%2BrG1%2Bg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Flipkart</t>
+          <t>HOK BEAUTY PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Performance Ads Specialist</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India</t>
+          <t>New Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2286,19 +2286,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/architect-at-flipkart-4442073191?position=1&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=UuVkxtYavjwIEq4Y%2BrG1%2Bg%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/performance-ads-specialist-at-hok-beauty-private-limited-4450587153?position=1&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=PcUoGdYWa6ILntNbYwpv%2Bw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HOK BEAUTY PRIVATE LIMITED</t>
+          <t>Webdaksha</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Performance Ads Specialist</t>
+          <t>Amazon/Flipkart- PPC Strategist/ PPC Executive- Pitampura, Delhi</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi, India</t>
+          <t>North Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2328,19 +2328,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/performance-ads-specialist-at-hok-beauty-private-limited-4450587153?position=1&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=PcUoGdYWa6ILntNbYwpv%2Bw%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/amazon-flipkart-ppc-strategist-ppc-executive-pitampura-delhi-at-webdaksha-4451122555?position=2&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=3s%2BdBBgPdc8c0V5UikltBA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Webdaksha</t>
+          <t>Zoom Into Web</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Amazon/Flipkart- PPC Strategist/ PPC Executive- Pitampura, Delhi</t>
+          <t>E-commerce Advertising Executive</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>North Delhi, Delhi, India</t>
+          <t>New Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2370,19 +2370,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/amazon-flipkart-ppc-strategist-ppc-executive-pitampura-delhi-at-webdaksha-4451122555?position=2&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=3s%2BdBBgPdc8c0V5UikltBA%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/e-commerce-advertising-executive-at-zoom-into-web-4453919429?position=4&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=veFAb%2F0e00z21QbrfkY5qw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Zoom Into Web</t>
+          <t>Luxury Personified</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>E-commerce Advertising Executive</t>
+          <t>Ecommerce Marketing Specialist (Amazon &amp; Flipkart)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi, India</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2412,19 +2412,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/e-commerce-advertising-executive-at-zoom-into-web-4453919429?position=4&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=veFAb%2F0e00z21QbrfkY5qw%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/ecommerce-marketing-specialist-amazon-flipkart-at-luxury-personified-4447777438?position=5&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=cBG%2F%2Bl%2B6l6kuaTYxEA1bCA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Luxury Personified</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ecommerce Marketing Specialist (Amazon &amp; Flipkart)</t>
+          <t>IN-Expert</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2454,34 +2454,34 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/ecommerce-marketing-specialist-amazon-flipkart-at-luxury-personified-4447777438?position=5&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=cBG%2F%2Bl%2B6l6kuaTYxEA1bCA%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/in-expert-at-apple-4453517632?position=6&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=VLmOJosgCakvG%2B%2FdLubkpQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Gintaa</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IN-Expert</t>
+          <t>Restaurant Onboarding Manager</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>New Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/in-expert-at-apple-4453517632?position=6&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=VLmOJosgCakvG%2B%2FdLubkpQ%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/restaurant-onboarding-manager-at-gintaa-4450437086?position=6&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=%2FOWrx6XIManVv2lb8cxzbQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi, India</t>
+          <t>Gurugram, Haryana, India</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2538,34 +2538,34 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/restaurant-onboarding-manager-at-gintaa-4450437086?position=6&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=%2FOWrx6XIManVv2lb8cxzbQ%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/restaurant-onboarding-manager-at-gintaa-4450436163?position=5&amp;pageNum=0&amp;refId=IlXJAMMUOJ5bmo4ZRFSLqg%3D%3D&amp;trackingId=pAgJZo6MH7WyBGHtyqRaWg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gintaa</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Restaurant Onboarding Manager</t>
+          <t>WHS Officer</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana, India</t>
+          <t>Janakpuri, Delhi, India</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2580,34 +2580,34 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/restaurant-onboarding-manager-at-gintaa-4450436163?position=5&amp;pageNum=0&amp;refId=IlXJAMMUOJ5bmo4ZRFSLqg%3D%3D&amp;trackingId=pAgJZo6MH7WyBGHtyqRaWg%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/whs-officer-at-amazon-4443007998?position=1&amp;pageNum=0&amp;refId=FQkQ8esI8YSTd58C7h5Q8A%3D%3D&amp;trackingId=60av%2FE6ppP6H9Md6Mbmy5Q%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gintaa</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Restaurant Onboarding Manager</t>
+          <t>WHS Officer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi, India</t>
+          <t>Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/restaurant-onboarding-manager-at-gintaa-4450437086?position=6&amp;pageNum=0&amp;refId=IlXJAMMUOJ5bmo4ZRFSLqg%3D%3D&amp;trackingId=DPU%2FOMIkihyFFAT%2FkgZoYw%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/whs-officer-at-amazon-4443029914?position=2&amp;pageNum=0&amp;refId=FQkQ8esI8YSTd58C7h5Q8A%3D%3D&amp;trackingId=vMRuqQ9hw1p7sHMt5m6mIg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2634,22 +2634,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WHS Officer</t>
+          <t>Cluster Manager, Amazon NOW</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Janakpuri, Delhi, India</t>
+          <t>Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2664,19 +2664,19 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/whs-officer-at-amazon-4443007998?position=1&amp;pageNum=0&amp;refId=FQkQ8esI8YSTd58C7h5Q8A%3D%3D&amp;trackingId=60av%2FE6ppP6H9Md6Mbmy5Q%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/cluster-manager-amazon-now-at-amazon-4447051994?position=4&amp;pageNum=0&amp;refId=FQkQ8esI8YSTd58C7h5Q8A%3D%3D&amp;trackingId=zDOUheZyMB%2BFVCkiwQpI3g%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WHS Officer</t>
+          <t>Account Technology Strategist - ITeS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Gurgaon, Haryana, India</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2706,19 +2706,19 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/whs-officer-at-amazon-4443029914?position=2&amp;pageNum=0&amp;refId=FQkQ8esI8YSTd58C7h5Q8A%3D%3D&amp;trackingId=vMRuqQ9hw1p7sHMt5m6mIg%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/account-technology-strategist-ites-at-microsoft-4454515543?position=2&amp;pageNum=0&amp;refId=j%2FK6Hlb%2F%2BicTmfvOYmOPcQ%3D%3D&amp;trackingId=Gj23HPKwdVxNbZQJ%2B8QxtQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WHS Officer</t>
+          <t>Sr. Account Technology Strategist - Mfg. &amp; Conglomerates</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Gurgaon, Haryana, India</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2748,34 +2748,34 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/whs-officer-at-amazon-4443026856?position=3&amp;pageNum=0&amp;refId=FQkQ8esI8YSTd58C7h5Q8A%3D%3D&amp;trackingId=kHDEIdkS2m19zT8YQSEzCQ%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/sr-account-technology-strategist-mfg-conglomerates-at-microsoft-4453110554?position=5&amp;pageNum=0&amp;refId=j%2FK6Hlb%2F%2BicTmfvOYmOPcQ%3D%3D&amp;trackingId=hNecc0ADX8fUUbuNwJ6SKQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cluster Manager, Amazon NOW</t>
+          <t>Policy Specialist</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Gurgaon, Haryana, India</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2790,34 +2790,34 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/cluster-manager-amazon-now-at-amazon-4447051994?position=4&amp;pageNum=0&amp;refId=FQkQ8esI8YSTd58C7h5Q8A%3D%3D&amp;trackingId=zDOUheZyMB%2BFVCkiwQpI3g%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/policy-specialist-at-google-4448543288?position=1&amp;pageNum=0&amp;refId=q2iENRSjQZHdUesa6IkfUA%3D%3D&amp;trackingId=sZ7patwPSZv3H6i71QvzVA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cluster Manager, Amazon NOW</t>
+          <t>Field Sales Representative</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Gurugram, Haryana, India</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2832,19 +2832,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/cluster-manager-amazon-now-at-amazon-4443040842?position=5&amp;pageNum=0&amp;refId=FQkQ8esI8YSTd58C7h5Q8A%3D%3D&amp;trackingId=749jqJF0yi8f6PQjU%2FWvdA%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/field-sales-representative-at-google-4435826900?position=2&amp;pageNum=0&amp;refId=q2iENRSjQZHdUesa6IkfUA%3D%3D&amp;trackingId=t7zVd%2Bh9tSJ9OUnhRJRLWw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Account Technology Strategist - ITeS</t>
+          <t>SDE2, CHEX</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gurgaon, Haryana, India</t>
+          <t>Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2874,34 +2874,34 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/account-technology-strategist-ites-at-microsoft-4454515543?position=2&amp;pageNum=0&amp;refId=j%2FK6Hlb%2F%2BicTmfvOYmOPcQ%3D%3D&amp;trackingId=Gj23HPKwdVxNbZQJ%2B8QxtQ%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/sde2-chex-at-amazon-4443042786?position=2&amp;pageNum=0&amp;refId=NA1Rue%2FX8rQTNSd9nLv4yA%3D%3D&amp;trackingId=kuW8NutywdmBzZ%2B%2FBYIUIw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ICC CHEMTEC PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sr. Account Technology Strategist - Mfg. &amp; Conglomerates</t>
+          <t>Flipkart Marketplace Growth Manager</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gurgaon, Haryana, India</t>
+          <t>South West Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/sr-account-technology-strategist-mfg-conglomerates-at-microsoft-4453110554?position=5&amp;pageNum=0&amp;refId=j%2FK6Hlb%2F%2BicTmfvOYmOPcQ%3D%3D&amp;trackingId=hNecc0ADX8fUUbuNwJ6SKQ%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/flipkart-marketplace-growth-manager-at-icc-chemtec-private-limited-4446413044?position=3&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=8u9Tv5iiP2pj6NMMK9aV7Q%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Gola Sizzlers</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Policy Specialist</t>
+          <t>Mixologist</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gurgaon, Haryana, India</t>
+          <t>New Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2953,39 +2953,39 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/policy-specialist-at-google-4448543288?position=1&amp;pageNum=0&amp;refId=q2iENRSjQZHdUesa6IkfUA%3D%3D&amp;trackingId=sZ7patwPSZv3H6i71QvzVA%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/mixologist-at-gola-sizzlers-4453573330?position=1&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=KmT95PXNW%2BG3ZXsidTUe0w%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Dil Foods</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Field Sales Representative</t>
+          <t>City Head - Restaurant Operations - Delhi NCR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana, India</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2995,24 +2995,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/field-sales-representative-at-google-4435826900?position=2&amp;pageNum=0&amp;refId=q2iENRSjQZHdUesa6IkfUA%3D%3D&amp;trackingId=t7zVd%2Bh9tSJ9OUnhRJRLWw%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/city-head-restaurant-operations-delhi-ncr-at-dil-foods-4451605943?position=2&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=UldnKpui8fNsb7wFxQJRgg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SDE2, CHEX</t>
+          <t>Commis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3037,39 +3037,39 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/sde2-chex-at-amazon-4443042786?position=2&amp;pageNum=0&amp;refId=NA1Rue%2FX8rQTNSd9nLv4yA%3D%3D&amp;trackingId=kuW8NutywdmBzZ%2B%2FBYIUIw%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/commis-at-marriott-international-4454515441?position=3&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=6d0AmIiR91bFRedWhg%2BY7Q%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ICC CHEMTEC PRIVATE LIMITED</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Flipkart Marketplace Growth Manager</t>
+          <t>F&amp;B and Event Service Expert</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>South West Delhi, Delhi, India</t>
+          <t>Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3084,19 +3084,19 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/flipkart-marketplace-growth-manager-at-icc-chemtec-private-limited-4446413044?position=3&amp;pageNum=0&amp;refId=TW3mmru68lBwzAv9gDFyZg%3D%3D&amp;trackingId=8u9Tv5iiP2pj6NMMK9aV7Q%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/f-b-and-event-service-expert-at-marriott-international-4452497895?position=4&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=AuM3gxI%2BLcbqUbLtPh55aA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Gola Sizzlers</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mixologist</t>
+          <t>F&amp;B ASSOCIATE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi, India</t>
+          <t>Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3126,34 +3126,34 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/mixologist-at-gola-sizzlers-4453573330?position=1&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=KmT95PXNW%2BG3ZXsidTUe0w%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/f-b-associate-at-hilton-4450300653?position=5&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=dyuadwyJc2UvQVYqt58wjA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dil Foods</t>
+          <t>Chai Point</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>City Head - Restaurant Operations - Delhi NCR</t>
+          <t>Team Member</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>Noida, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3168,19 +3168,19 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/city-head-restaurant-operations-delhi-ncr-at-dil-foods-4451605943?position=2&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=UldnKpui8fNsb7wFxQJRgg%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/team-member-at-chai-point-4450791521?position=1&amp;pageNum=0&amp;refId=IlXJAMMUOJ5bmo4ZRFSLqg%3D%3D&amp;trackingId=mDk8ryUXJeviBHnjPPPx%2BA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Chai Point</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Commis</t>
+          <t>Team Member</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Gurgaon, Haryana, India</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3210,29 +3210,29 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/commis-at-marriott-international-4454515441?position=3&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=6d0AmIiR91bFRedWhg%2BY7Q%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/team-member-at-chai-point-4447601827?position=2&amp;pageNum=0&amp;refId=IlXJAMMUOJ5bmo4ZRFSLqg%3D%3D&amp;trackingId=tpAhfoX351n5Pzklda%2FeCQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Instamart</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>F&amp;B and Event Service Expert</t>
+          <t>Account Manager</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3252,29 +3252,29 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/f-b-and-event-service-expert-at-marriott-international-4452497895?position=4&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=AuM3gxI%2BLcbqUbLtPh55aA%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/account-manager-at-instamart-4437460825?position=3&amp;pageNum=0&amp;refId=IlXJAMMUOJ5bmo4ZRFSLqg%3D%3D&amp;trackingId=8mPQxgHFdOVsV15H8gdmlQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>F&amp;B ASSOCIATE</t>
+          <t>SDE II , Stores TA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Fresher / Entry-Level (0-1 yrs)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-1 yrs (Fresher / New Grad)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3294,19 +3294,19 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/f-b-associate-at-hilton-4450300653?position=5&amp;pageNum=0&amp;refId=TeRG2AeY79ZVZ1zOCI%2Bnzg%3D%3D&amp;trackingId=dyuadwyJc2UvQVYqt58wjA%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/sde-ii-stores-ta-at-amazon-4443047443?position=4&amp;pageNum=0&amp;refId=NA1Rue%2FX8rQTNSd9nLv4yA%3D%3D&amp;trackingId=Qt1Iv5XIpLH4PLgNgRv0ag%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Chai Point</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Team Member</t>
+          <t>Automation engineer (Warehouse Automation)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh, India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3331,39 +3331,39 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/team-member-at-chai-point-4450791521?position=1&amp;pageNum=0&amp;refId=IlXJAMMUOJ5bmo4ZRFSLqg%3D%3D&amp;trackingId=mDk8ryUXJeviBHnjPPPx%2BA%3D%3D</t>
+          <t>https://jobs.lever.co/meesho/fe839191-1761-4094-9d3c-4d554904b84d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Chai Point</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Team Member</t>
+          <t>Assistant Manager Finance – Logistics Intelligence</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gurgaon, Haryana, India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3373,24 +3373,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/team-member-at-chai-point-4447601827?position=2&amp;pageNum=0&amp;refId=IlXJAMMUOJ5bmo4ZRFSLqg%3D%3D&amp;trackingId=tpAhfoX351n5Pzklda%2FeCQ%3D%3D</t>
+          <t>https://jobs.lever.co/meesho/3032374b-0010-4d19-8dd1-26c37c396cba</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Instamart</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Account Manager</t>
+          <t>Associate Director — Industry Intelligence &amp; Benchmarking</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3415,24 +3415,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/account-manager-at-instamart-4437460825?position=3&amp;pageNum=0&amp;refId=IlXJAMMUOJ5bmo4ZRFSLqg%3D%3D&amp;trackingId=8mPQxgHFdOVsV15H8gdmlQ%3D%3D</t>
+          <t>https://jobs.lever.co/meesho/9251a5a3-041e-49a1-b3a8-9db1ba22989a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dil Foods</t>
+          <t>Flipkart</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>City Head - Restaurant Operations - Delhi NCR</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>Greater Bengaluru Area</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3457,39 +3457,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/city-head-restaurant-operations-delhi-ncr-at-dil-foods-4451605943?position=4&amp;pageNum=0&amp;refId=IlXJAMMUOJ5bmo4ZRFSLqg%3D%3D&amp;trackingId=6qiV97sk%2Fl41j0V6XwU7QA%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/senior-ai-architect-at-flipkart-4449704021?position=2&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=jFMwsqiwptfF464IzvK2Dg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Mongodb</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SDE II , Stores TA</t>
+          <t>Account Development Representative</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fresher / Entry-Level (0-1 yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0-1 yrs (Fresher / New Grad)</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3499,24 +3499,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/sde-ii-stores-ta-at-amazon-4443047443?position=4&amp;pageNum=0&amp;refId=NA1Rue%2FX8rQTNSd9nLv4yA%3D%3D&amp;trackingId=Qt1Iv5XIpLH4PLgNgRv0ag%3D%3D</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7318466</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Mongodb</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Automation engineer (Warehouse Automation)</t>
+          <t>Account Development Representative</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3541,39 +3541,39 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/fe839191-1761-4094-9d3c-4d554904b84d</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7318558</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Cred</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Assistant Manager Finance – Logistics Intelligence</t>
+          <t>business development &amp; partnerships</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>bengaluru</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3583,24 +3583,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/3032374b-0010-4d19-8dd1-26c37c396cba</t>
+          <t>https://jobs.lever.co/cred/09022710-e79a-4cf0-8060-df0e1cd64263</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Cred</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Associate Director — Industry Intelligence &amp; Benchmarking</t>
+          <t>business development &amp; partnerships – commercial lead</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>bengaluru</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3625,39 +3625,39 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/9251a5a3-041e-49a1-b3a8-9db1ba22989a</t>
+          <t>https://jobs.lever.co/cred/b532b595-bc8d-4b51-a2e6-7228ef1cabfc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Flipkart</t>
+          <t>Cred</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>growth and business - max and wallet</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Greater Bengaluru Area</t>
+          <t>bengaluru</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3667,24 +3667,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/senior-ai-architect-at-flipkart-4449704021?position=2&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=jFMwsqiwptfF464IzvK2Dg%3D%3D</t>
+          <t>https://jobs.lever.co/cred/37f0a1b9-e5a1-45de-ada6-f8363bb877f6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mongodb</t>
+          <t>Cred</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Account Development Representative</t>
+          <t>web developer - Prefr</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>hyderabad</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3714,34 +3714,34 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7318466</t>
+          <t>https://jobs.lever.co/cred/58dfc330-090b-4318-a395-cc7280cf5065</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mongodb</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Account Development Representative</t>
+          <t>AM/ Manager - Risk &amp; Decision Science</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3756,34 +3756,34 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7318558</t>
+          <t>https://jobs.lever.co/meesho/7d9af9b5-c1c7-48ec-bbb5-9b25e49f6596</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cred</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>business development &amp; partnerships</t>
+          <t>Assistant Manager - Business Finance</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>bengaluru</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3798,19 +3798,19 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/cred/09022710-e79a-4cf0-8060-df0e1cd64263</t>
+          <t>https://jobs.lever.co/meesho/22c4a7a0-43be-439e-9473-2f8074b3e8d5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cred</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>business development &amp; partnerships – commercial lead</t>
+          <t>Assistant Manager - Ops</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>bengaluru</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3840,34 +3840,34 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/cred/b532b595-bc8d-4b51-a2e6-7228ef1cabfc</t>
+          <t>https://jobs.lever.co/meesho/5afe596f-17a2-4e8b-a498-ca46b2c7a869</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cred</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>growth and business - max and wallet</t>
+          <t>Assistant Manager - Taxation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>bengaluru</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3882,34 +3882,34 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/cred/37f0a1b9-e5a1-45de-ada6-f8363bb877f6</t>
+          <t>https://jobs.lever.co/meesho/49b47b8e-6ed5-4b72-9310-c69a49113b40</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cred</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>web developer - Prefr</t>
+          <t>Assistant Manager – HR</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>hyderabad</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/cred/58dfc330-090b-4318-a395-cc7280cf5065</t>
+          <t>https://jobs.lever.co/meesho/8cd64fd4-4ed2-4aac-bd5a-9407d3685445</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AM/ Manager - Risk &amp; Decision Science</t>
+          <t>Associate Compliance Manager</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/7d9af9b5-c1c7-48ec-bbb5-9b25e49f6596</t>
+          <t>https://jobs.lever.co/meesho/80ab7795-de6b-4dfe-9a66-a8ad5e7b8a83</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Assistant Manager - Business Finance</t>
+          <t>Associate Director - Business Finance</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/22c4a7a0-43be-439e-9473-2f8074b3e8d5</t>
+          <t>https://jobs.lever.co/meesho/b7f20190-5e8c-4cbc-901a-44a05bfec9be</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Assistant Manager - Ops</t>
+          <t>Associate Director - Sort center Design &amp; Operations – Sort Center Automation​</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/5afe596f-17a2-4e8b-a498-ca46b2c7a869</t>
+          <t>https://jobs.lever.co/meesho/b50e3cdc-439d-467c-8e4d-a87d339c4974</t>
         </is>
       </c>
     </row>
@@ -4062,17 +4062,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Assistant Manager - Taxation</t>
+          <t>Architect - Android</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4087,39 +4087,39 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/49b47b8e-6ed5-4b72-9310-c69a49113b40</t>
+          <t>https://jobs.lever.co/meesho/040a5a75-28d2-4b56-904b-071c41d4ea90</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Cred</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Assistant Manager – HR</t>
+          <t>copywriter - kuvera</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>bengaluru</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4129,39 +4129,39 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/8cd64fd4-4ed2-4aac-bd5a-9407d3685445</t>
+          <t>https://jobs.lever.co/cred/24c4782a-e2d7-42a0-990d-e8ebd174ab57</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Flipkart</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Associate Compliance Manager</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4171,39 +4171,39 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/80ab7795-de6b-4dfe-9a66-a8ad5e7b8a83</t>
+          <t>https://in.linkedin.com/jobs/view/artificial-intelligence-engineer-at-flipkart-4446761837?position=6&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=wabQy%2Bryw%2B6IALyB2asDcA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Cred</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Associate Director - Business Finance</t>
+          <t>fund settlements</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>bengaluru</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4213,220 +4213,10 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/meesho/b7f20190-5e8c-4cbc-901a-44a05bfec9be</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Meesho</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Associate Director - Sort center Design &amp; Operations – Sort Center Automation​</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Senior / Lead (5+ yrs)</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>5+ yrs</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Competitive (Market Standard)</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/meesho/b50e3cdc-439d-467c-8e4d-a87d339c4974</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Meesho</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Architect - Android</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Full-Time (General)</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>1-3 yrs (Standard)</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Competitive (Market Standard)</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/meesho/040a5a75-28d2-4b56-904b-071c41d4ea90</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Cred</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>copywriter - kuvera</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Full-Time (General)</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>1-3 yrs (Standard)</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>bengaluru</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Competitive (Market Standard)</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/cred/24c4782a-e2d7-42a0-990d-e8ebd174ab57</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Flipkart</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Full-Time (General)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>1-3 yrs (Standard)</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Bengaluru, Karnataka, India</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Competitive (Market Standard)</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>56%</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>https://in.linkedin.com/jobs/view/artificial-intelligence-engineer-at-flipkart-4446761837?position=6&amp;pageNum=0&amp;refId=e67QbQWVug42WOIng0qkhA%3D%3D&amp;trackingId=wabQy%2Bryw%2B6IALyB2asDcA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Cred</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>fund settlements</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Full-Time (General)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>1-3 yrs (Standard)</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>bengaluru</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Competitive (Market Standard)</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/cred/7aba55a4-0457-47b7-bb49-9d9ecf514cc1</t>
         </is>
@@ -4443,10 +4233,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
@@ -9457,27 +9247,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Account Executive, Bridge </t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SF, NYC, SEA, CHI</t>
+          <t>Mason, OH</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -9492,34 +9282,34 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8077887</t>
+          <t>https://www.linkedin.com/jobs/view/software-development-engineer-at-workday-4432331549?position=1&amp;pageNum=0&amp;refId=8oY6BSRYkymFrZscRn2FMw%3D%3D&amp;trackingId=16cnIWIniWoS5Aj5LmvVdQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Midmark Corporation</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Account Executive, Bridge (Stripe Crypto and Stablecoins)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9534,34 +9324,34 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8023928</t>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-at-midmark-corporation-4413573803?position=2&amp;pageNum=0&amp;refId=8oY6BSRYkymFrZscRn2FMw%3D%3D&amp;trackingId=tfjK8ZRHThS%2F5mULrS6UkA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Siemens Digital Industries Software</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Account Executive, Commercial (Grower)</t>
+          <t>Software Engineer, Performance &amp; Optimization - US Hybrid OH/MI</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Milford, OH</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -9576,34 +9366,34 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8123027</t>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-performance-optimization-us-hybrid-oh-mi-at-siemens-digital-industries-software-4424518261?position=3&amp;pageNum=0&amp;refId=8oY6BSRYkymFrZscRn2FMw%3D%3D&amp;trackingId=GxR2qVeuwr%2BC%2Fwqhs2zTUA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Siemens Digital Industries Software</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Account Executive, Commercial Grower (Japanese Fluency)</t>
+          <t>Software Engineer, Performance &amp; Optimization - US Hybrid OH/MI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -9618,34 +9408,34 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8042978</t>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-performance-optimization-us-hybrid-oh-mi-at-siemens-digital-industries-software-4393081933?position=4&amp;pageNum=0&amp;refId=8oY6BSRYkymFrZscRn2FMw%3D%3D&amp;trackingId=Sun2PFrYTxovj65%2B%2Bdureg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Soundtrace</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Account Executive, Commercial Hunter (Japanese Fluency)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9660,34 +9450,35 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7789539</t>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-at-soundtrace-4450929343?position=5&amp;pageNum=0&amp;refId=8oY6BSRYkymFrZscRn2FMw%3D%3D&amp;trackingId=RPYvjo8tEXaxWnMA%2F4qCqA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Beltways</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Account Executive, Cross Border China</t>
+          <t>Software
+Engineer III</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Hebron, KY</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9702,34 +9493,34 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7893199</t>
+          <t>https://www.linkedin.com/jobs/view/software%0Aengineer-iii-at-beltways-4450914719?position=6&amp;pageNum=0&amp;refId=8oY6BSRYkymFrZscRn2FMw%3D%3D&amp;trackingId=qZ5u%2BIFObFrEz3sZ3Vseyg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>ODW Logistics</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Account Executive, Crypto/Stablecoins </t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Hamilton, OH</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -9744,34 +9535,34 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8041076</t>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-ii-at-odw-logistics-4415685167?position=7&amp;pageNum=0&amp;refId=8oY6BSRYkymFrZscRn2FMw%3D%3D&amp;trackingId=J34KkW0l9B%2BJK0rvpo9Xug%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Superalloy Manufacturing Solutions Corporation</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Account Executive, Enterprise (Canada) </t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA-Toronto, CA-Montreal, CA-Vancouver </t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -9786,34 +9577,34 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8119822</t>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-at-superalloy-manufacturing-solutions-corporation-4443163038?position=8&amp;pageNum=0&amp;refId=8oY6BSRYkymFrZscRn2FMw%3D%3D&amp;trackingId=XGlfY4DgjGFEiFkIz2vFbw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Medpace</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Account Executive - Enterprise, Growth</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>US-San Francisco, US-California, US-Chicago</t>
+          <t>Cincinnati, OH</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -9828,34 +9619,34 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7997146</t>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-at-medpace-4345390049?position=9&amp;pageNum=0&amp;refId=8oY6BSRYkymFrZscRn2FMw%3D%3D&amp;trackingId=FETaG%2BySrcfYvPWvL6%2FhuQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Formbox</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Account Executive, Emerging Enterprise (Berlin, Germany)</t>
+          <t>Clojure Engineer</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Ohio County, IN</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -9870,34 +9661,34 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5364702004?gh_jid=5364702004</t>
+          <t>https://www.linkedin.com/jobs/view/clojure-engineer-at-formbox-4454072097?position=10&amp;pageNum=0&amp;refId=8oY6BSRYkymFrZscRn2FMw%3D%3D&amp;trackingId=313G17VXYhyM620OUFEEQw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Radiance Technologies</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Account Executive, Enterprise</t>
+          <t>Software Engineer with Security Clearance</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>San Francisco, CA • New York, NY • United States</t>
+          <t>Bellbrook, OH</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -9912,34 +9703,34 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5426468004?gh_jid=5426468004</t>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-with-security-clearance-at-radiance-technologies-4429943202?position=1&amp;pageNum=1&amp;refId=NXkCujbGrs5L4dfrqNw4wA%3D%3D&amp;trackingId=YJXrKF7s3wR6V1D5m2K%2FCw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Cryptic Vector</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Account Executive, Enterprise (Berlin, Germany)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Full-Time</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Miamisburg, OH</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -9954,19 +9745,19 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5783812004?gh_jid=5783812004</t>
+          <t>https://www.linkedin.com/jobs/view/full-stack-developer-at-cryptic-vector-4416978020?position=2&amp;pageNum=1&amp;refId=NXkCujbGrs5L4dfrqNw4wA%3D%3D&amp;trackingId=dZQBd5ZWfR6i1u0PJPXVWw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Account Executive, Enterprise (Paris, France) </t>
+          <t xml:space="preserve">Account Executive, Bridge </t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9981,7 +9772,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t>SF, NYC, SEA, CHI</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -9996,19 +9787,19 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5428656004?gh_jid=5428656004</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8077887</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Account Executive, Enterprise (Singapore)</t>
+          <t>Account Executive, Bridge (Stripe Crypto and Stablecoins)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -10023,7 +9814,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -10038,19 +9829,19 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5753209004?gh_jid=5753209004</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8023928</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Account Executive, Enterprise (Sydney or Melbourne, Australia)</t>
+          <t>Account Executive, Commercial (Grower)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10065,7 +9856,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sydney, Australia • Melbourne, Australia</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -10080,19 +9871,19 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5803515004?gh_jid=5803515004</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8123027</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Account Executive, Enterprise (Tokyo, Japan) </t>
+          <t>Account Executive, Commercial Grower (Japanese Fluency)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10107,7 +9898,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -10122,19 +9913,19 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5806875004?gh_jid=5806875004</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8042978</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Account Executive, Federal - Civilian</t>
+          <t>Account Executive, Commercial Hunter (Japanese Fluency)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -10149,7 +9940,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -10164,34 +9955,34 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6143113004?gh_jid=6143113004</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7789539</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Account Executive, Mid-Market</t>
+          <t>Account Executive, Cross Border China</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Experienced (2-4 yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2-4 yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>San Francisco, CA • New York, NY • United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -10206,34 +9997,34 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5422236004?gh_jid=5422236004</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7893199</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Account Executive, Mid-Market (London, United Kingdom)</t>
+          <t xml:space="preserve">Account Executive, Crypto/Stablecoins </t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Experienced (2-4 yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2-4 yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>London, England</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -10248,34 +10039,34 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5415515004?gh_jid=5415515004</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8041076</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Account Executive, Mid-Market (Paris, France)</t>
+          <t xml:space="preserve">Account Executive, Enterprise (Canada) </t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Experienced (2-4 yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2-4 yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t xml:space="preserve">CA-Toronto, CA-Montreal, CA-Vancouver </t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -10290,34 +10081,34 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5844225004?gh_jid=5844225004</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8119822</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Acquisition Manager</t>
+          <t>Account Executive - Enterprise, Growth</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Berlin, Germany </t>
+          <t>US-San Francisco, US-California, US-Chicago</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -10332,34 +10123,34 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7995153?gh_jid=7995153</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7997146</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Acquisition Manager</t>
+          <t>Account Executive, Emerging Enterprise (Berlin, Germany)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -10374,34 +10165,34 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7995199?gh_jid=7995199</t>
+          <t>https://boards.greenhouse.io/figma/jobs/5364702004?gh_jid=5364702004</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Business Operations and Growth Lead</t>
+          <t>Account Executive, Enterprise</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sydney, Australia</t>
+          <t>San Francisco, CA • New York, NY • United States</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -10416,34 +10207,34 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7999656?gh_jid=7999656</t>
+          <t>https://boards.greenhouse.io/figma/jobs/5426468004?gh_jid=5426468004</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Business Operations and Growth Lead</t>
+          <t>Account Executive, Enterprise (Berlin, Germany)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States </t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -10458,19 +10249,19 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7834481?gh_jid=7834481</t>
+          <t>https://boards.greenhouse.io/figma/jobs/5783812004?gh_jid=5783812004</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Compensation Partner</t>
+          <t xml:space="preserve">Account Executive, Enterprise (Paris, France) </t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10485,7 +10276,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>San Francisco, United States</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -10500,19 +10291,19 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8104102?gh_jid=8104102</t>
+          <t>https://boards.greenhouse.io/figma/jobs/5428656004?gh_jid=5428656004</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Postman</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Account Development Representative</t>
+          <t>Account Executive, Enterprise (Singapore)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10527,7 +10318,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -10542,19 +10333,19 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/postman/jobs/7452188003</t>
+          <t>https://boards.greenhouse.io/figma/jobs/5753209004?gh_jid=5753209004</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Postman</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Account Development Representative, Bahasa Speaking</t>
+          <t>Account Executive, Enterprise (Sydney or Melbourne, Australia)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10569,7 +10360,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>Sydney, Australia • Melbourne, Australia</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -10584,19 +10375,19 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/postman/jobs/7817966003</t>
+          <t>https://boards.greenhouse.io/figma/jobs/5803515004?gh_jid=5803515004</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Postman</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Account Development Representative, German Speaking</t>
+          <t xml:space="preserve">Account Executive, Enterprise (Tokyo, Japan) </t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10611,7 +10402,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -10626,19 +10417,19 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/postman/jobs/7560630003</t>
+          <t>https://boards.greenhouse.io/figma/jobs/5806875004?gh_jid=5806875004</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Postman</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Account Executive, Federal - Civilian</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10653,7 +10444,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>New York, New York, United States</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -10668,34 +10459,34 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/postman/jobs/7824502003</t>
+          <t>https://boards.greenhouse.io/figma/jobs/6143113004?gh_jid=6143113004</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ソリューションアーキテクト (プリセールス)</t>
+          <t>Account Executive, Mid-Market</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Experienced (2-4 yrs)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>2-4 yrs</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>San Francisco, CA • New York, NY • United States</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -10710,34 +10501,34 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8559344002</t>
+          <t>https://boards.greenhouse.io/figma/jobs/5422236004?gh_jid=5422236004</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Agency Lead</t>
+          <t>Account Executive, Mid-Market (London, United Kingdom)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Experienced (2-4 yrs)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>2-4 yrs</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>New York, NY, US</t>
+          <t>London, England</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -10752,34 +10543,34 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8022863</t>
+          <t>https://boards.greenhouse.io/figma/jobs/5415515004?gh_jid=5415515004</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Agency Lead</t>
+          <t>Account Executive, Mid-Market (Paris, France)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Experienced (2-4 yrs)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>2-4 yrs</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -10794,19 +10585,19 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8010505</t>
+          <t>https://boards.greenhouse.io/figma/jobs/5844225004?gh_jid=5844225004</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Agency Lead, Independents</t>
+          <t>Acquisition Manager</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10821,7 +10612,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles, CA, US; Chicago, IL, US; New York, NY, US </t>
+          <t xml:space="preserve">Berlin, Germany </t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -10836,19 +10627,19 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8089344</t>
+          <t>https://careers.airbnb.com/positions/7995153?gh_jid=7995153</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Client Account Manager, CPG Enterprise (French Market)</t>
+          <t>Acquisition Manager</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10863,7 +10654,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dublin, IE</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -10878,19 +10669,19 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8037865</t>
+          <t>https://careers.airbnb.com/positions/7995199?gh_jid=7995199</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Client Account Manager, Enterprise Nordics (English Speaking)</t>
+          <t>Business Operations and Growth Lead</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10905,7 +10696,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Dublin, IE</t>
+          <t>Sydney, Australia</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -10920,34 +10711,34 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8075678</t>
+          <t>https://careers.airbnb.com/positions/7999656?gh_jid=7999656</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Client Account Manager, Enterprise Sales (International Retail)</t>
+          <t>Business Operations and Growth Lead</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>0 yrs (College / Student)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Dublin, IE</t>
+          <t xml:space="preserve">United States </t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -10962,34 +10753,34 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8016712</t>
+          <t>https://careers.airbnb.com/positions/7834481?gh_jid=7834481</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Client Account Manager II</t>
+          <t>Compensation Partner</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>São Paulo, BR</t>
+          <t>San Francisco, United States</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -11004,34 +10795,34 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8081335</t>
+          <t>https://careers.airbnb.com/positions/8104102?gh_jid=8104102</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Postman</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Client Account Manager II</t>
+          <t>Account Development Representative</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>São Paulo, BR</t>
+          <t>Boston, Massachusetts</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -11046,34 +10837,34 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8081337</t>
+          <t>https://job-boards.greenhouse.io/postman/jobs/7452188003</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Postman</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Client Account Manager II (12 Months Fixed Term)</t>
+          <t>Account Development Representative, Bahasa Speaking</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -11088,19 +10879,19 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8102744</t>
+          <t>https://job-boards.greenhouse.io/postman/jobs/7817966003</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Postman</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Account Maintenance Associate</t>
+          <t>Account Development Representative, German Speaking</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -11115,7 +10906,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Clearwater, FL</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -11130,19 +10921,19 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8114351?t=gh_src=&amp;gh_jid=8114351</t>
+          <t>https://job-boards.greenhouse.io/postman/jobs/7560630003</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Postman</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Assistant General Counsel, Canada</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -11157,7 +10948,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Toronto, Canada</t>
+          <t>New York, New York, United States</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -11172,19 +10963,19 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8093267?t=gh_src=&amp;gh_jid=8093267</t>
+          <t>https://job-boards.greenhouse.io/postman/jobs/7824502003</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Assistant General Counsel, Credit Cards</t>
+          <t>ソリューションアーキテクト (プリセールス)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -11199,7 +10990,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY; Washington, DC</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -11214,34 +11005,34 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/7943204?t=gh_src=&amp;gh_jid=7943204</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8559344002</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Assistant General Counsel, Regulatory</t>
+          <t>Agency Lead</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY; Washington, DC</t>
+          <t>New York, NY, US</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -11256,19 +11047,19 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8003458?t=gh_src=&amp;gh_jid=8003458</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8022863</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Chief of Staff, Brokerage Product</t>
+          <t>Agency Lead</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -11283,7 +11074,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Menlo Park, CA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -11298,19 +11089,19 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/7839130?t=gh_src=&amp;gh_jid=7839130</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8010505</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Compliance Advisory Lead, Money</t>
+          <t>Agency Lead, Independents</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -11325,7 +11116,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY; Washington, DC</t>
+          <t xml:space="preserve">Los Angeles, CA, US; Chicago, IL, US; New York, NY, US </t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -11340,19 +11131,19 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8054481?t=gh_src=&amp;gh_jid=8054481</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8089344</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Compliance Senior Specialist</t>
+          <t>Client Account Manager, CPG Enterprise (French Market)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -11367,7 +11158,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Chicago, IL; Denver, CO; Lake Mary, FL; New York, NY</t>
+          <t>Dublin, IE</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -11382,19 +11173,19 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8077870?t=gh_src=&amp;gh_jid=8077870</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8037865</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Account Manager, Advertising Solutions</t>
+          <t>Client Account Manager, Enterprise Nordics (English Speaking)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11409,7 +11200,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco Bay Area </t>
+          <t>Dublin, IE</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -11424,34 +11215,34 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/discord/jobs/8599937002</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8075678</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Associate Product Counsel, Safety</t>
+          <t>Client Account Manager, Enterprise Sales (International Retail)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>0 yrs (College / Student)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area</t>
+          <t>Dublin, IE</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -11466,19 +11257,19 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/discord/jobs/8625545002</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8016712</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Commercial Policy Lead, Brand Safety &amp; Malware</t>
+          <t>Client Account Manager II</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -11493,7 +11284,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco Bay Area </t>
+          <t>São Paulo, BR</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -11508,34 +11299,34 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/discord/jobs/8680047002</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8081335</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Gusto</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Benefits Care Advocate, Phoenix </t>
+          <t>Client Account Manager II (12 Months Fixed Term)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Phoenix, Arizona, United States</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -11550,34 +11341,34 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8055761</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8102744</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Gusto</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Compliance Manager, Broker-Dealer &amp; Investment Adviser</t>
+          <t>Account Maintenance Associate</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Denver, CO;San Francisco, CA;New York, NY</t>
+          <t>Clearwater, FL</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -11592,19 +11383,19 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8024433</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8114351?t=gh_src=&amp;gh_jid=8114351</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Gusto</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Employee Relations Partner</t>
+          <t>Assistant General Counsel, Canada</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -11619,7 +11410,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Toronto, Canada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -11634,34 +11425,34 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/7961009</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8093267?t=gh_src=&amp;gh_jid=8093267</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Gusto</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Event Marketing Manager</t>
+          <t>Assistant General Counsel, Credit Cards</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ;Denver, CO;San Francisco, CA</t>
+          <t>Menlo Park, CA; New York, NY; Washington, DC</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -11676,19 +11467,19 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8094350</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/7943204?t=gh_src=&amp;gh_jid=7943204</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Mongodb</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Account Development Representative</t>
+          <t>Assistant General Counsel, Regulatory</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11703,7 +11494,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Menlo Park, CA; New York, NY; Washington, DC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -11718,34 +11509,34 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7318049</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8003458?t=gh_src=&amp;gh_jid=8003458</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Mongodb</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Account Development Representative</t>
+          <t>Chief of Staff, Brokerage Product</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Menlo Park, CA</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -11760,34 +11551,34 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7311234</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/7839130?t=gh_src=&amp;gh_jid=7839130</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Mongodb</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Account Development Representative</t>
+          <t>Compliance Advisory Lead, Money</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Dublin, Ireland</t>
+          <t>Menlo Park, CA; New York, NY; Washington, DC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -11802,34 +11593,34 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8081378</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8054481?t=gh_src=&amp;gh_jid=8054481</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Mongodb</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Account Development Representative - English Speaking</t>
+          <t>Compliance Senior Specialist</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Chicago, IL; Denver, CO; Lake Mary, FL; New York, NY</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -11844,34 +11635,34 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8079914</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8077870?t=gh_src=&amp;gh_jid=8077870</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Mongodb</t>
+          <t>Discord</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Account Development Representative, German Speaking</t>
+          <t>Account Manager, Advertising Solutions</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t xml:space="preserve">San Francisco Bay Area </t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -11886,34 +11677,34 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7337287</t>
+          <t>https://job-boards.greenhouse.io/discord/jobs/8599937002</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Discord</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Advertiser Solutions Vendor Lead - Programmatic and Direct Support</t>
+          <t>Associate Product Counsel, Safety</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>San Francisco Bay Area</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -11928,39 +11719,39 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/890b2c0f-f46f-4a4b-bb73-3a6af6e0edd5</t>
+          <t>https://job-boards.greenhouse.io/discord/jobs/8625545002</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Discord</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Android Engineer - Advertising</t>
+          <t>Commercial Policy Lead, Brand Safety &amp; Malware</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t xml:space="preserve">San Francisco Bay Area </t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>$107,483 / yr</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -11970,19 +11761,19 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/a0fa7da3-4c3c-4fa2-97bd-7d6eb01eb9e5</t>
+          <t>https://job-boards.greenhouse.io/discord/jobs/8680047002</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Gusto</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Android Engineer - Subscriptions</t>
+          <t xml:space="preserve">Benefits Care Advocate, Phoenix </t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11997,7 +11788,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Phoenix, Arizona, United States</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -12012,19 +11803,19 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/b4ad9572-e20f-4185-a284-99d9740d04f0</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/8055761</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Gusto</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Artist &amp; Label Partnerships Manager, Maghreb</t>
+          <t>Compliance Manager, Broker-Dealer &amp; Investment Adviser</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -12039,7 +11830,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Denver, CO;San Francisco, CA;New York, NY</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -12054,34 +11845,34 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/ddb5dfa9-c5ef-4199-bd19-c179af568cc8</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/8024433</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Gusto</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Artist Label Partnerships Manager, Taiwan</t>
+          <t>Employee Relations Partner</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -12096,34 +11887,34 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/77526d53-3811-4336-9c0d-72f6ac0242c7</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/7961009</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Gusto</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Associate Client Partner - Emerging &amp; Scaled (New Business, German Speaking)</t>
+          <t>Event Marketing Manager</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Scottsdale, AZ;Denver, CO;San Francisco, CA</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -12138,19 +11929,19 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/d5628547-6362-470e-8828-7ab565054eaa</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/8094350</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Mongodb</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Associate Client Partner, Emerging &amp; Scaled</t>
+          <t>Account Development Representative</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -12165,12 +11956,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>$67,433 - $96,333 / yr</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -12180,39 +11971,39 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/da93b18f-3f08-49d1-8725-15b5b70cb75c</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7318049</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Mongodb</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Associate Director, Portfolio &amp; Monetization Architecture</t>
+          <t>Account Development Representative</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>$191,274 - $273,249 / yr</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -12222,19 +12013,19 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/7aeec299-4653-4c5d-aafb-d537e1232208</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7311234</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Mongodb</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Client Partner - Emerging &amp; Scaled (German Speaking)</t>
+          <t>Account Development Representative</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -12249,7 +12040,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Dublin, Ireland</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -12264,34 +12055,34 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/3895bc9e-ca1c-433c-8604-b58ae84aa577</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8081378</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Mongodb</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Client Account Manager I</t>
+          <t>Account Development Representative - English Speaking</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Buenos Aires, AR</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -12301,39 +12092,39 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8089250</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8079914</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Mongodb</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Client Account Manager II, CPG (Nestle)</t>
+          <t>Account Development Representative, German Speaking</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>New York, NY, US</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -12343,39 +12134,39 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8085092</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7337287</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Support Engineer (AMER)</t>
+          <t>Advertiser Solutions Vendor Lead - Programmatic and Direct Support</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>3+ yrs</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -12385,24 +12176,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/e4e3ccb7-7b7d-42a2-be0f-26cbb5ae4abd/application</t>
+          <t>https://jobs.lever.co/spotify/890b2c0f-f46f-4a4b-bb73-3a6af6e0edd5</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Support Engineer (APAC)</t>
+          <t>Android Engineer - Advertising</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12412,39 +12203,39 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>3+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>$107,483 / yr</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/142135ae-a15f-4ec7-90bb-cb4e7968bc09/application</t>
+          <t>https://jobs.lever.co/spotify/a0fa7da3-4c3c-4fa2-97bd-7d6eb01eb9e5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Support Engineer (AMER - Weekends)</t>
+          <t>Android Engineer - Subscriptions</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12454,12 +12245,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>3+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -12469,39 +12260,39 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/dcf09dfe-55bc-44ba-b5db-1a2de7f33216/application</t>
+          <t>https://jobs.lever.co/spotify/b4ad9572-e20f-4185-a284-99d9740d04f0</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Support Engineer (EMEA - Weekends)</t>
+          <t>Artist &amp; Label Partnerships Manager, Maghreb</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>3+ yrs</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -12511,24 +12302,24 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/590a0742-97f1-47f4-81a2-567efc939ae2/application</t>
+          <t>https://jobs.lever.co/spotify/ddb5dfa9-c5ef-4199-bd19-c179af568cc8</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, AI</t>
+          <t>Artist Label Partnerships Manager, Taiwan</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12538,39 +12329,39 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>4+ yrs</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>San Francisco, California</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>$155,000 / yr</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sentry/81f09568-da7d-4ed1-8283-614f846c9b00/application</t>
+          <t>https://jobs.lever.co/spotify/77526d53-3811-4336-9c0d-72f6ac0242c7</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Multigres Deployment Engineer</t>
+          <t>Associate Client Partner - Emerging &amp; Scaled (New Business, German Speaking)</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12585,7 +12376,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -12595,24 +12386,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/f035bda1-b5d3-4c5b-8736-b9c335fe1c3b/application</t>
+          <t>https://jobs.lever.co/spotify/d5628547-6362-470e-8828-7ab565054eaa</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Customer Solution Architect (AMER)</t>
+          <t>Associate Client Partner, Emerging &amp; Scaled</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12627,76 +12418,76 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>$67,433 - $96,333 / yr</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/d5573afa-636c-4219-832f-386f498243bf/application</t>
+          <t>https://jobs.lever.co/spotify/da93b18f-3f08-49d1-8725-15b5b70cb75c</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Developer Relations Engineer (San Francisco, CA)</t>
+          <t>Associate Director, Portfolio &amp; Monetization Architecture</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>$191,274 - $273,249 / yr</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/a1320bbf-bfae-49a8-a1b7-12eeccaf39ca/application</t>
+          <t>https://jobs.lever.co/spotify/7aeec299-4653-4c5d-aafb-d537e1232208</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Customer Solution Architect (EMEA)</t>
+          <t>Client Partner - Emerging &amp; Scaled (German Speaking)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12711,7 +12502,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -12721,39 +12512,39 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/c3099780-60d5-4b8a-ab08-c701d114cf62/application</t>
+          <t>https://jobs.lever.co/spotify/3895bc9e-ca1c-433c-8604-b58ae84aa577</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GTM Strategist</t>
+          <t>Client Account Manager I</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>6+ yrs</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Buenos Aires, AR</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -12763,39 +12554,39 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/23a39e2b-333a-438c-b4e6-cf7cdde27e78/application</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8089250</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GTM Systems Engineer, Salesforce</t>
+          <t>Client Account Manager II, CPG (Nestle)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>7+ yrs</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>New York, NY (HQ)</t>
+          <t>New York, NY, US</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -12805,66 +12596,66 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/ramp/ffc09fc0-7785-48db-a203-a148f62534be/application</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8085092</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI</t>
+          <t>Support Engineer (AMER)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>3+ yrs</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>San Francisco, California</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>$155,000 / yr</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sentry/6eb8d5f2-977e-4ff4-bdbe-fccb8747b5d7/application</t>
+          <t>https://jobs.ashbyhq.com/supabase/e4e3ccb7-7b7d-42a2-be0f-26cbb5ae4abd/application</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Openai</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Software Engineer, Developer Productivity</t>
+          <t>Support Engineer (APAC)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12874,12 +12665,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>3+ yrs</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -12889,66 +12680,66 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/2cba0d45-7a4f-4f38-ac73-3f8633bf0349/application</t>
+          <t>https://jobs.ashbyhq.com/supabase/142135ae-a15f-4ec7-90bb-cb4e7968bc09/application</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI Evals</t>
+          <t>Support Engineer (AMER - Weekends)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>3+ yrs</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>San Francisco, California</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>$155,000 / yr</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sentry/95d2eeab-291d-40ad-97a2-86b104f3c7ad/application</t>
+          <t>https://jobs.ashbyhq.com/supabase/dcf09dfe-55bc-44ba-b5db-1a2de7f33216/application</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Openai</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Training: ML Framework Engineer</t>
+          <t>Support Engineer (EMEA - Weekends)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12958,12 +12749,12 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>3+ yrs</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -12973,81 +12764,81 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/d8794980-1d3f-4d82-8b48-811449b6c492/application</t>
+          <t>https://jobs.ashbyhq.com/supabase/590a0742-97f1-47f4-81a2-567efc939ae2/application</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Openai</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Staff Machine Learning Engineer, AI</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>3+ yrs</t>
+          <t>4+ yrs</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Francisco, California</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>$155,000 / yr</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/fc5bbc77-a30c-4e7a-9acc-8a2e748545b4/application</t>
+          <t>https://jobs.ashbyhq.com/sentry/81f09568-da7d-4ed1-8283-614f846c9b00/application</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Senior / Staff Product Engineer</t>
+          <t>Multigres Deployment Engineer</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -13057,39 +12848,39 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/linear/069c4628-88d7-4e4d-b393-c996fc7f3076/application</t>
+          <t>https://jobs.ashbyhq.com/supabase/f035bda1-b5d3-4c5b-8736-b9c335fe1c3b/application</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Senior / Staff Product Engineer, AI</t>
+          <t>Customer Solution Architect (AMER)</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -13099,39 +12890,39 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/linear/b4a7764e-c680-4bdf-9956-dc78f2ca94d5/application</t>
+          <t>https://jobs.ashbyhq.com/supabase/d5573afa-636c-4219-832f-386f498243bf/application</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Senior / Staff Fullstack Engineer</t>
+          <t>Developer Relations Engineer (San Francisco, CA)</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -13141,39 +12932,39 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/linear/cd5ae036-0223-427a-b038-ba16ef9dcb32/application</t>
+          <t>https://jobs.ashbyhq.com/supabase/a1320bbf-bfae-49a8-a1b7-12eeccaf39ca/application</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Senior / Staff Product Engineer</t>
+          <t>Customer Solution Architect (EMEA)</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -13183,24 +12974,24 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/linear/12f8f208-0b9c-4569-bb3d-41c8a197029e/application</t>
+          <t>https://jobs.ashbyhq.com/supabase/c3099780-60d5-4b8a-ab08-c701d114cf62/application</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>GTM Strategist</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13210,12 +13001,12 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2-5 yrs</t>
+          <t>6+ yrs</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -13225,39 +13016,39 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/linear/0c7c2e26-0a98-42cf-a47c-9a3999fb513b/application</t>
+          <t>https://jobs.ashbyhq.com/supabase/23a39e2b-333a-438c-b4e6-cf7cdde27e78/application</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Senior / Staff Fullstack Engineer</t>
+          <t>GTM Systems Engineer, Salesforce</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>7+ yrs</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>New York, NY (HQ)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -13267,24 +13058,24 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/linear/d3bc1ced-3ce4-4086-a050-555055dbb1ff/application</t>
+          <t>https://jobs.ashbyhq.com/ramp/ffc09fc0-7785-48db-a203-a148f62534be/application</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, iOS</t>
+          <t>Senior Software Engineer, AI</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13299,34 +13090,34 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>New York, NY (HQ)</t>
+          <t>San Francisco, California</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>$155,000 / yr</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/ramp/0ed80a29-6cca-42d7-b7e0-066d4fa7b37f/application</t>
+          <t>https://jobs.ashbyhq.com/sentry/6eb8d5f2-977e-4ff4-bdbe-fccb8747b5d7/application</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Openai</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Software Engineer, Developer Productivity</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13336,12 +13127,12 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>3+ yrs</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>San Francisco, California</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -13351,29 +13142,29 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sentry/9889cf59-cd32-4aff-bff7-645bb1be4e14/application</t>
+          <t>https://jobs.ashbyhq.com/openai/2cba0d45-7a4f-4f38-ac73-3f8633bf0349/application</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Security Engineer, Cloud</t>
+          <t>Senior Software Engineer, AI Evals</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13383,34 +13174,34 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>New York, NY (HQ)</t>
+          <t>San Francisco, California</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>$10,000 / yr</t>
+          <t>$155,000 / yr</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/ramp/34413f8d-26bf-4bbc-8ade-eb309a0e2245/application</t>
+          <t>https://jobs.ashbyhq.com/sentry/95d2eeab-291d-40ad-97a2-86b104f3c7ad/application</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Openai</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>American Tech Fellowship</t>
+          <t>Training: ML Framework Engineer</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13420,12 +13211,12 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -13435,24 +13226,24 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/0ccbe620-a3ef-41d1-a5c4-68e56b3c91d0</t>
+          <t>https://jobs.ashbyhq.com/openai/d8794980-1d3f-4d82-8b48-811449b6c492/application</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Openai</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Mobile Engineer, Android</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13462,12 +13253,12 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>1+ yrs</t>
+          <t>3+ yrs</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>New York, NY (HQ)</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -13477,39 +13268,39 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/ramp/f564dcf9-9390-4a3f-896f-8047a5086040/application</t>
+          <t>https://jobs.ashbyhq.com/openai/fc5bbc77-a30c-4e7a-9acc-8a2e748545b4/application</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Mobile Engineer, iOS</t>
+          <t>Senior / Staff Product Engineer</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>1+ yrs</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>New York, NY (HQ)</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -13519,39 +13310,39 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/ramp/4859cd5e-f2a9-44d7-81f7-8bfc0e62369f/application</t>
+          <t>https://jobs.ashbyhq.com/linear/069c4628-88d7-4e4d-b393-c996fc7f3076/application</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Openai</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Research Engineer</t>
+          <t>Senior / Staff Product Engineer, AI</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -13561,39 +13352,39 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/240d459b-696d-43eb-8497-fab3e56ecd9b/application</t>
+          <t>https://jobs.ashbyhq.com/linear/b4a7764e-c680-4bdf-9956-dc78f2ca94d5/application</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Openai</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Research Engineer, Retrieval &amp; Search, Applied Engineering</t>
+          <t>Senior / Staff Fullstack Engineer</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -13603,39 +13394,39 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/7322d344-9325-4a92-8445-0a2c4e9272f8/application</t>
+          <t>https://jobs.ashbyhq.com/linear/cd5ae036-0223-427a-b038-ba16ef9dcb32/application</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Openai</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Software Engineer, RL Training Infra</t>
+          <t>Senior / Staff Product Engineer</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -13645,24 +13436,24 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/13995549-e8cc-498f-9eaa-1869067ac35b/application</t>
+          <t>https://jobs.ashbyhq.com/linear/12f8f208-0b9c-4569-bb3d-41c8a197029e/application</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Openai</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13672,12 +13463,12 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>4+ yrs</t>
+          <t>2-5 yrs</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -13687,39 +13478,39 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/f763c6b3-5167-4a67-b691-4c3fa2c44156/application</t>
+          <t>https://jobs.ashbyhq.com/linear/0c7c2e26-0a98-42cf-a47c-9a3999fb513b/application</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Openai</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software Engineer, Data Acquisition </t>
+          <t>Senior / Staff Fullstack Engineer</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>4+ yrs</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -13729,29 +13520,29 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/41d9d129-2e58-4ad3-be81-2e5096f4da4d/application</t>
+          <t>https://jobs.ashbyhq.com/linear/d3bc1ced-3ce4-4086-a050-555055dbb1ff/application</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>GTM Recruiter, AMER</t>
+          <t>Staff Software Engineer, iOS</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -13761,7 +13552,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>San Francisco, California</t>
+          <t>New York, NY (HQ)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -13771,24 +13562,24 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/f663839e-46ac-44ad-9720-da2b6aa28093/application</t>
+          <t>https://jobs.ashbyhq.com/ramp/0ed80a29-6cca-42d7-b7e0-066d4fa7b37f/application</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Product Support Specialist, Pacific/Mountain Time</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13798,12 +13589,12 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>3+ yrs</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>San Francisco, California</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -13813,12 +13604,12 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/linear/d062065e-05bb-42ce-a430-ec205695cc2e/application</t>
+          <t>https://jobs.ashbyhq.com/sentry/9889cf59-cd32-4aff-bff7-645bb1be4e14/application</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13621,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Software Engineer, Frontend</t>
+          <t xml:space="preserve"> Security Engineer, Cloud</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13840,7 +13631,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2+ yrs</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -13855,39 +13646,39 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/ramp/4e64ab86-4e30-403b-b1b9-41dc052570ce/application</t>
+          <t>https://jobs.ashbyhq.com/ramp/34413f8d-26bf-4bbc-8ade-eb309a0e2245/application</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Technical Program Manager</t>
+          <t>American Tech Fellowship</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>2+ yrs</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>New York, NY (HQ)</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -13897,39 +13688,39 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/ramp/1db75064-e38c-4b21-8310-21471943d0be/application</t>
+          <t>https://jobs.lever.co/palantir/0ccbe620-a3ef-41d1-a5c4-68e56b3c91d0</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Openai</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Account Director - Tokyo</t>
+          <t>Mobile Engineer, Android</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>7+ yrs</t>
+          <t>1+ yrs</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>New York, NY (HQ)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -13939,24 +13730,24 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/18f58952-c242-4562-8732-073a0ae8029e/application</t>
+          <t>https://jobs.ashbyhq.com/ramp/f564dcf9-9390-4a3f-896f-8047a5086040/application</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Openai</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Researcher, Robustness &amp; Safety Training</t>
+          <t>Mobile Engineer, iOS</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -13966,12 +13757,12 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>4+ yrs</t>
+          <t>1+ yrs</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York, NY (HQ)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -13981,24 +13772,24 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/2560ed50-5535-42b8-b069-9ebc28ce7493/application</t>
+          <t>https://jobs.ashbyhq.com/ramp/4859cd5e-f2a9-44d7-81f7-8bfc0e62369f/application</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Openai</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Business Development Representative, San Francisco</t>
+          <t>Research Engineer</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14013,7 +13804,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>San Francisco, California</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -14023,24 +13814,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/b21fef72-4864-4a3e-a627-91557a0f8a36/application</t>
+          <t>https://jobs.ashbyhq.com/openai/240d459b-696d-43eb-8497-fab3e56ecd9b/application</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Openai</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Business Development Representative, Japan</t>
+          <t>Research Engineer, Retrieval &amp; Search, Applied Engineering</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14055,7 +13846,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tokyo, Japan </t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -14065,39 +13856,39 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/c64a2cda-4c84-45bd-823d-f9141c316733/application</t>
+          <t>https://jobs.ashbyhq.com/openai/7322d344-9325-4a92-8445-0a2c4e9272f8/application</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Openai</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Sales Operations Lead, AMER</t>
+          <t>Software Engineer, RL Training Infra</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>San Francisco, California</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -14107,24 +13898,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/cb4f5e1a-88e4-4259-b73c-ac975dbcde5f/application</t>
+          <t>https://jobs.ashbyhq.com/openai/13995549-e8cc-498f-9eaa-1869067ac35b/application</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Openai</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Model Behavior Engineer</t>
+          <t>Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14134,12 +13925,12 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>4+ yrs</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>New York, New York</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -14149,71 +13940,71 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/4bbfad88-0830-46c5-8d05-d95d17d583ca/application</t>
+          <t>https://jobs.ashbyhq.com/openai/f763c6b3-5167-4a67-b691-4c3fa2c44156/application</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Openai</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Senior Enterprise Product Marketing Manager</t>
+          <t xml:space="preserve">Software Engineer, Data Acquisition </t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>4-6 yrs</t>
+          <t>4+ yrs</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>San Francisco, California</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>$150,000 / yr</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sentry/d96096f1-f662-4581-8706-2f088bc43211/application</t>
+          <t>https://jobs.ashbyhq.com/openai/41d9d129-2e58-4ad3-be81-2e5096f4da4d/application</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Senior Developer Experience Engineer</t>
+          <t>GTM Recruiter, AMER</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -14233,39 +14024,39 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sentry/7ed2b263-3873-44c6-a730-2ca96100c58f/application</t>
+          <t>https://jobs.ashbyhq.com/notion/f663839e-46ac-44ad-9720-da2b6aa28093/application</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Frameworks), JavaScript SDK</t>
+          <t>Product Support Specialist, Pacific/Mountain Time</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>1-3 yrs (Standard)</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Toronto, Ontario, Canada</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -14280,39 +14071,39 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sentry/bbd40ef1-c1d5-4e0e-99dd-30fde87cc804/application</t>
+          <t>https://jobs.ashbyhq.com/linear/d062065e-05bb-42ce-a430-ec205695cc2e/application</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (iOS), SDK</t>
+          <t>Software Engineer, Frontend</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Senior / Lead (5+ yrs)</t>
+          <t>Full-Time (General)</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>5+ yrs</t>
+          <t>2+ yrs</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Toronto, Ontario, Canada</t>
+          <t>New York, NY (HQ)</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>$10,000 / yr</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -14322,7 +14113,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sentry/37c30441-078e-4575-83e9-d955ca2e15ce/application</t>
+          <t>https://jobs.ashbyhq.com/ramp/4e64ab86-4e30-403b-b1b9-41dc052570ce/application</t>
         </is>
       </c>
     </row>
@@ -14334,17 +14125,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Credit Risk Associate</t>
+          <t>Technical Program Manager</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Full-Time (General)</t>
+          <t>Senior / Lead (5+ yrs)</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>1-3 yrs (Standard)</t>
+          <t>5+ yrs</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -14359,52 +14150,514 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/ramp/4745807e-82f4-4b1a-857c-dc8dadc73076/application</t>
+          <t>https://jobs.ashbyhq.com/ramp/1db75064-e38c-4b21-8310-21471943d0be/application</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Account Director - Tokyo</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Senior / Lead (5+ yrs)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>7+ yrs</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Tokyo, Japan</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/openai/18f58952-c242-4562-8732-073a0ae8029e/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Researcher, Robustness &amp; Safety Training</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Full-Time (General)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>4+ yrs</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/openai/2560ed50-5535-42b8-b069-9ebc28ce7493/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Business Development Representative, San Francisco</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Full-Time (General)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>1-3 yrs (Standard)</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>San Francisco, California</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/notion/b21fef72-4864-4a3e-a627-91557a0f8a36/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Business Development Representative, Japan</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Full-Time (General)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>1-3 yrs (Standard)</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo, Japan </t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/notion/c64a2cda-4c84-45bd-823d-f9141c316733/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Sales Operations Lead, AMER</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Senior / Lead (5+ yrs)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>5+ yrs</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>San Francisco, California</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/notion/cb4f5e1a-88e4-4259-b73c-ac975dbcde5f/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Model Behavior Engineer</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Full-Time (General)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>1-3 yrs (Standard)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>New York, New York</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/notion/4bbfad88-0830-46c5-8d05-d95d17d583ca/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Sentry</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Senior Enterprise Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Senior / Lead (5+ yrs)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>4-6 yrs</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>San Francisco, California</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>$150,000 / yr</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sentry/d96096f1-f662-4581-8706-2f088bc43211/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Sentry</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Senior Developer Experience Engineer</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Senior / Lead (5+ yrs)</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>5+ yrs</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>San Francisco, California</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sentry/7ed2b263-3873-44c6-a730-2ca96100c58f/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Sentry</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Frameworks), JavaScript SDK</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Senior / Lead (5+ yrs)</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>5+ yrs</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sentry/bbd40ef1-c1d5-4e0e-99dd-30fde87cc804/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Sentry</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (iOS), SDK</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Senior / Lead (5+ yrs)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>5+ yrs</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sentry/37c30441-078e-4575-83e9-d955ca2e15ce/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Credit Risk Associate</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Full-Time (General)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>1-3 yrs (Standard)</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>New York, NY (HQ)</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/ramp/4745807e-82f4-4b1a-857c-dc8dadc73076/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
         <is>
           <t>Product Designer</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Full-Time (General)</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>1-3 yrs (Standard)</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Full-Time (General)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>1-3 yrs (Standard)</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
         <is>
           <t>New York, NY (HQ)</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>Competitive (Market Standard)</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
+      <c r="H248" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/ramp/eca54d0e-232a-4c3e-bfcc-d6c6add393f5/application</t>
         </is>

--- a/data/helios_jobs_two_tabs.xlsx
+++ b/data/helios_jobs_two_tabs.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -786,12 +786,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Accenture in India</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Razorpay)</t>
+          <t>Custom Software Engineer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -801,37 +801,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 08, 2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟡 AGING</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4454591390?position=1&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=ArzemHDxFnemBL291umnmA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Accenture in India</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (BrowserStack)</t>
+          <t>Custom Software Engineer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -868,37 +868,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Nagpur, Maharashtra, India</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 07, 2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>10d</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟡 AGING</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4448374964?position=2&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=Sblf5B5GG59xm%2B4C4TwKYA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>YouthNet</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Microsoft India)</t>
+          <t>Software Developer Job Vacancy in Kohima Nagaland</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Kohima, Nagaland, India</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 06, 2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>11d</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟡 AGING</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -980,19 +980,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-developer-job-vacancy-in-kohima-nagaland-at-youthnet-4247411794?position=3&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=PBEN9oTHtxysOxLG1e45OQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>ServLogic Innovations LLP.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Atlassian)</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1002,37 +1002,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Port Blair, Andaman and Nicobar Islands, India</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Jul 28, 2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟠 STALE</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1047,19 +1047,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/senior-net-developer-at-servlogic-innovations-llp-4446990115?position=5&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=S102FtHUL%2B4XfY8vleUNcg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Marduk Technologies</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Postman)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1069,37 +1069,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Pocket 6 Sector 21, Delhi, India</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Aug 16, 2026</t>
+          <t>Jul 27, 2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟠 STALE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1114,19 +1114,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-developer-at-marduk-technologies-4449817611?position=6&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=8BSgfiq%2FVRdXcAHEzm9Ryg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NeonScouts</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Krutrim AI)</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1136,37 +1136,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Anupgarh, Rajasthan, India</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Aug 16, 2026</t>
+          <t>Jul 26, 2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟠 STALE</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1181,19 +1181,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/priya-sharma-at-neonscouts-4445853567?position=7&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=A8A%2BuAJnlWwObh5Bm0Rgmw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Amazon India)</t>
+          <t>Software Developer 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1203,37 +1203,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Trivandrum, Kerala, India</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Aug 16, 2026</t>
+          <t>Jul 04, 2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>44d</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🔴 VERY STALE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1248,59 +1248,59 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-developer-3-at-oracle-4438722956?position=8&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=NZcvnFuRB8m2i2DcD%2FcYNQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software Engineer, Infrastructure </t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Hyderabad, India</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Salesforce India)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Aug 16, 2026</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1315,59 +1315,59 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.ashbyhq.com/notion/42f18ccd-c4c8-4a85-8c1f-de12c575fe87/application</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Charles Schwab India</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Software Developer (Dot Net)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Sarvam AI)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Aug 15, 2026</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1382,59 +1382,59 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-developer-dot-net-at-charles-schwab-india-4443282262?position=3&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=oLVzB%2FhKLjgkBZuPk%2BdcyQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>SourcingXPress</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Pine Labs)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Aug 15, 2026</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1449,59 +1449,59 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-at-sourcingxpress-4368177937?position=4&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=2Z%2F5PTc1jAzPj7OUEzgCdQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pune Division, Maharashtra, India</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (NVIDIA India)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Aug 15, 2026</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1516,59 +1516,59 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-at-autodesk-4450348403?position=5&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=nFxbMhmNfBr7z9TftZQVrA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>CloudBees</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Software Engineer - Golang</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Oracle India)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Aug 15, 2026</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1583,19 +1583,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-golang-at-cloudbees-4455278546?position=6&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=kLD4P7BqioxnvhjNUPJnzA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Clearwater Analytics</t>
+          <t>SourcingXPress</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mumbai Metropolitan Region</t>
+          <t>Chennai, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1620,22 +1620,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Aug 15, 2026</t>
+          <t>Recent</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1650,59 +1650,59 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-development-engineer-at-clearwater-analytics-4450330786?position=1&amp;pageNum=1&amp;refId=u61WPYQrHvSOHNn5R%2BiqiA%3D%3D&amp;trackingId=gcJQ%2BFhcq5cziu%2BUR1CObA%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-at-sourcingxpress-4416232418?position=7&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=Y9KXPgMGydDFv3NaXBVPsg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Application Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (CRED)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3d</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1717,59 +1717,59 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/application-software-engineer-2-at-oracle-4445020407?position=8&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=WD1lwljBH8EgA89y7753xA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Application Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Trivandrum, Kerala, India</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Zerodha)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3d</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1784,59 +1784,59 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/application-software-engineer-2-at-oracle-4445037375?position=9&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=Qi2%2FoMH2Ru3wsVcfWboohg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Walmart Global Tech India</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SOFTWARE ENGINEER III</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Intel India)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3d</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1851,59 +1851,59 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-iii-at-walmart-global-tech-india-4401949760?position=10&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=Yrf1BURHBOrE7VudUd4RXw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Addepar</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pune District, Maharashtra, India</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Cisco India)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3d</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-at-addepar-4451526400?position=2&amp;pageNum=1&amp;refId=un0n5dcspQ2AFk%2FvdLjKiA%3D%3D&amp;trackingId=WWL8uuzTuVw%2Fedj%2B7X2AqA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Meesho)</t>
+          <t>Software Engineer / AI Systems (Razorpay)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Paytm)</t>
+          <t>Software Engineer / AI Systems (BrowserStack)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (AMD India)</t>
+          <t>Software Engineer / AI Systems (Microsoft India)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2126,12 +2126,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Devolity</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Software Engineer / AI Systems (Atlassian)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/sr-azure-cloud-engineer-at-devolity-4404850484?position=4&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=IgK6vAIKucjrQJ0LLni7ew%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Groww)</t>
+          <t>Software Engineer / AI Systems (Postman)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 16, 2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (PhonePe)</t>
+          <t>Software Engineer / AI Systems (Krutrim AI)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 16, 2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Adobe India)</t>
+          <t>Software Engineer / AI Systems (Amazon India)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 16, 2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (InMobi)</t>
+          <t>Software Engineer / AI Systems (Salesforce India)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Aug 11, 2026</t>
+          <t>Aug 16, 2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Uber India)</t>
+          <t>Software Engineer / AI Systems (Sarvam AI)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Aug 11, 2026</t>
+          <t>Aug 15, 2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2528,12 +2528,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Software Engineer, Developer Experience</t>
+          <t>Software Engineer / AI Systems (Pine Labs)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2543,32 +2543,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Aug 11, 2026</t>
+          <t>Aug 15, 2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2588,19 +2588,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/49bdf081-6e20-4323-8c73-6d6b19544ff5/application</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Accenture in India</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Custom Software Engineer</t>
+          <t>Software Engineer / AI Systems (NVIDIA India)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2610,37 +2610,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Aug 08, 2026</t>
+          <t>Aug 15, 2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4454591390?position=1&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=ArzemHDxFnemBL291umnmA%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Flipkart)</t>
+          <t>Software Engineer / AI Systems (Oracle India)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Aug 08, 2026</t>
+          <t>Aug 15, 2026</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2729,12 +2729,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Accenture in India</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Custom Software Engineer</t>
+          <t>Software Engineer / AI Systems (CRED)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2744,37 +2744,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nagpur, Maharashtra, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Aug 07, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4448374964?position=2&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=Sblf5B5GG59xm%2B4C4TwKYA%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Swiggy)</t>
+          <t>Software Engineer / AI Systems (Zerodha)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Aug 07, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2863,12 +2863,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>YouthNet</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Software Developer Job Vacancy in Kohima Nagaland</t>
+          <t>Software Engineer / AI Systems (Intel India)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2878,37 +2878,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kohima, Nagaland, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Aug 06, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-developer-job-vacancy-in-kohima-nagaland-at-youthnet-4247411794?position=3&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=PBEN9oTHtxysOxLG1e45OQ%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Zomato)</t>
+          <t>Software Engineer / AI Systems (Cisco India)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2965,17 +2965,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Aug 06, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ServLogic Innovations LLP.</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Software Engineer / AI Systems (Meesho)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3012,37 +3012,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Port Blair, Andaman and Nicobar Islands, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Jul 28, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/senior-net-developer-at-servlogic-innovations-llp-4446990115?position=5&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=S102FtHUL%2B4XfY8vleUNcg%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Samsung R&amp;D India)</t>
+          <t>Software Engineer / AI Systems (Paytm)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3099,17 +3099,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Jul 28, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3131,12 +3131,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marduk Technologies</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer / AI Systems (AMD India)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3146,37 +3146,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pocket 6 Sector 21, Delhi, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-developer-at-marduk-technologies-4449817611?position=6&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=8BSgfiq%2FVRdXcAHEzm9Ryg%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (LG Electronics R&amp;D)</t>
+          <t>Software Engineer / AI Systems (Groww)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3265,12 +3265,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NeonScouts</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Priya Sharma</t>
+          <t>Software Engineer / AI Systems (PhonePe)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3280,37 +3280,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Anupgarh, Rajasthan, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Jul 26, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/priya-sharma-at-neonscouts-4445853567?position=7&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=A8A%2BuAJnlWwObh5Bm0Rgmw%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Nokia India)</t>
+          <t>Software Engineer / AI Systems (Adobe India)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3367,17 +3367,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Jul 26, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3399,12 +3399,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Software Developer 3</t>
+          <t>Software Engineer / AI Systems (InMobi)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3414,37 +3414,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trivandrum, Kerala, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Jul 04, 2026</t>
+          <t>Aug 11, 2026</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>44d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>🔴 VERY STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-developer-3-at-oracle-4438722956?position=8&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=NZcvnFuRB8m2i2DcD%2FcYNQ%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Google India)</t>
+          <t>Software Engineer / AI Systems (Uber India)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3501,17 +3501,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Jul 04, 2026</t>
+          <t>Aug 11, 2026</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>44d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>🔴 VERY STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3533,67 +3533,804 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (Flipkart)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Aug 08, 2026</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>9d</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>🟡 AGING</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (Swiggy)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Aug 07, 2026</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10d</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>🟡 AGING</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (Zomato)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Aug 06, 2026</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>11d</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>🟡 AGING</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (Samsung R&amp;D India)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Jul 28, 2026</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20d</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>🟠 STALE</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (LG Electronics R&amp;D)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Jul 27, 2026</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>21d</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>🟠 STALE</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (Nokia India)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Jul 26, 2026</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>22d</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>🟠 STALE</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (Google India)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Jul 04, 2026</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>44d</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>🔴 VERY STALE</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Clearwater Analytics</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Mumbai Metropolitan Region</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Aug 15, 2026</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>🟢 FRESH</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/software-development-engineer-at-clearwater-analytics-4450330786?position=1&amp;pageNum=1&amp;refId=u61WPYQrHvSOHNn5R%2BiqiA%3D%3D&amp;trackingId=gcJQ%2BFhcq5cziu%2BUR1CObA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Devolity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sr. Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Delhi, Delhi, India</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4d</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>🟢 FRESH</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/sr-azure-cloud-engineer-at-devolity-4404850484?position=4&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=IgK6vAIKucjrQJ0LLni7ew%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Software Engineer, Infrastructure </t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Software Engineer, Developer Experience</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>0-2 yrs</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Hyderabad, India</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Competitive (Market Standard)</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>🟢 FRESH</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/notion/49bdf081-6e20-4323-8c73-6d6b19544ff5/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WebEngage</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>Recent</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>⚪ UNKNOWN</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>CONFIRMED_POSTED</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>❌ NO</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/notion/42f18ccd-c4c8-4a85-8c1f-de12c575fe87/application</t>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-java-at-webengage-4261040176?position=1&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=%2FZU90nGJGeudtfryQPTBSw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Charles Schwab India</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Software Developer (Java)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>⚪ UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/software-developer-java-at-charles-schwab-india-4443274661?position=2&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=swSmGS3lpWeK7fsyDX5OPg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3608,7 +4345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3827,6 +4564,73 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Xerox</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SOFTWARE ENGINEER 3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Greater Kolkata Area</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>⚪ UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-3-at-xerox-4362193461?position=1&amp;pageNum=1&amp;refId=un0n5dcspQ2AFk%2FvdLjKiA%3D%3D&amp;trackingId=F%2FvlHHSkgq0fsvWnMMYFEQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3838,7 +4642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -4194,12 +4998,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Accenture in India</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Razorpay)</t>
+          <t>Custom Software Engineer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4209,37 +5013,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 08, 2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟡 AGING</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4254,19 +5058,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4454591390?position=1&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=ArzemHDxFnemBL291umnmA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Accenture in India</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (BrowserStack)</t>
+          <t>Custom Software Engineer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4276,37 +5080,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Nagpur, Maharashtra, India</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 07, 2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>10d</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟡 AGING</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4321,19 +5125,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4448374964?position=2&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=Sblf5B5GG59xm%2B4C4TwKYA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>YouthNet</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Microsoft India)</t>
+          <t>Software Developer Job Vacancy in Kohima Nagaland</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4343,37 +5147,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Kohima, Nagaland, India</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 06, 2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>11d</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟡 AGING</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -4388,19 +5192,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-developer-job-vacancy-in-kohima-nagaland-at-youthnet-4247411794?position=3&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=PBEN9oTHtxysOxLG1e45OQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>ServLogic Innovations LLP.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Atlassian)</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4410,37 +5214,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Port Blair, Andaman and Nicobar Islands, India</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Jul 28, 2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟠 STALE</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4455,19 +5259,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/senior-net-developer-at-servlogic-innovations-llp-4446990115?position=5&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=S102FtHUL%2B4XfY8vleUNcg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Marduk Technologies</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Postman)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4477,37 +5281,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Pocket 6 Sector 21, Delhi, India</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Aug 16, 2026</t>
+          <t>Jul 27, 2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟠 STALE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4522,19 +5326,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-developer-at-marduk-technologies-4449817611?position=6&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=8BSgfiq%2FVRdXcAHEzm9Ryg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NeonScouts</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Krutrim AI)</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4544,37 +5348,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Anupgarh, Rajasthan, India</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Aug 16, 2026</t>
+          <t>Jul 26, 2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🟠 STALE</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4589,19 +5393,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/priya-sharma-at-neonscouts-4445853567?position=7&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=A8A%2BuAJnlWwObh5Bm0Rgmw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Amazon India)</t>
+          <t>Software Developer 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4611,37 +5415,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1-3 yrs</t>
+          <t>0-2 yrs</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
+          <t>Trivandrum, Kerala, India</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Competitive (Market Standard)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Aug 16, 2026</t>
+          <t>Jul 04, 2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>44d</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>🔴 VERY STALE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4656,59 +5460,59 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-developer-3-at-oracle-4438722956?position=8&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=NZcvnFuRB8m2i2DcD%2FcYNQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software Engineer, Infrastructure </t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Hyderabad, India</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Salesforce India)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Aug 16, 2026</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4723,19 +5527,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.ashbyhq.com/notion/42f18ccd-c4c8-4a85-8c1f-de12c575fe87/application</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Soft Solutions</t>
+          <t>Charles Schwab India</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Developer (Dot Net)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4750,7 +5554,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Greater Lucknow Area</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4760,22 +5564,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Aug 16, 2026</t>
+          <t>Recent</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4790,59 +5594,59 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-developer-at-soft-solutions-4306120377?position=10&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=O9loeVXlEh8YatYRtS416Q%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/software-developer-dot-net-at-charles-schwab-india-4443282262?position=3&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=oLVzB%2FhKLjgkBZuPk%2BdcyQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>SourcingXPress</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Sarvam AI)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Aug 15, 2026</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4857,59 +5661,59 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-at-sourcingxpress-4368177937?position=4&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=2Z%2F5PTc1jAzPj7OUEzgCdQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pune Division, Maharashtra, India</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Pine Labs)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Aug 15, 2026</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4924,59 +5728,59 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-at-autodesk-4450348403?position=5&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=nFxbMhmNfBr7z9TftZQVrA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>CloudBees</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Software Engineer - Golang</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (NVIDIA India)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Aug 15, 2026</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4991,59 +5795,59 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-golang-at-cloudbees-4455278546?position=6&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=kLD4P7BqioxnvhjNUPJnzA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>SourcingXPress</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Oracle India)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Aug 15, 2026</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5058,19 +5862,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-at-sourcingxpress-4416232418?position=7&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=Y9KXPgMGydDFv3NaXBVPsg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Clearwater Analytics</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Application Software Engineer 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5085,7 +5889,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mumbai Metropolitan Region</t>
+          <t>Chennai, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5095,22 +5899,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Aug 15, 2026</t>
+          <t>Recent</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5125,59 +5929,59 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-development-engineer-at-clearwater-analytics-4450330786?position=1&amp;pageNum=1&amp;refId=u61WPYQrHvSOHNn5R%2BiqiA%3D%3D&amp;trackingId=gcJQ%2BFhcq5cziu%2BUR1CObA%3D%3D</t>
+          <t>https://in.linkedin.com/jobs/view/application-software-engineer-2-at-oracle-4445020407?position=8&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=WD1lwljBH8EgA89y7753xA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Application Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Trivandrum, Kerala, India</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (CRED)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3d</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5192,59 +5996,59 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/application-software-engineer-2-at-oracle-4445037375?position=9&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=Qi2%2FoMH2Ru3wsVcfWboohg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Walmart Global Tech India</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SOFTWARE ENGINEER III</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Zerodha)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3d</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5259,59 +6063,59 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-iii-at-walmart-global-tech-india-4401949760?position=10&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=Yrf1BURHBOrE7VudUd4RXw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Addepar</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pune District, Maharashtra, India</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Software Engineer / AI Systems (Intel India)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1-3 yrs</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>India (Bangalore / Gurgaon / Remote)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3d</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>🟢 FRESH</t>
+          <t>⚪ UNKNOWN</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -5326,7 +6130,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-at-addepar-4451526400?position=2&amp;pageNum=1&amp;refId=un0n5dcspQ2AFk%2FvdLjKiA%3D%3D&amp;trackingId=WWL8uuzTuVw%2Fedj%2B7X2AqA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5338,7 +6142,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Cisco India)</t>
+          <t>Software Engineer / AI Systems (Razorpay)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5368,12 +6172,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -5400,12 +6204,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fullscreens</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Full-Stack Engineers</t>
+          <t>Software Engineer / AI Systems (BrowserStack)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5415,32 +6219,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Greater Kolkata Area</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -5460,7 +6264,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/full-stack-engineers-at-fullscreens-4448951607?position=2&amp;pageNum=1&amp;refId=u61WPYQrHvSOHNn5R%2BiqiA%3D%3D&amp;trackingId=obhzqIBnMqveUruzIWMesQ%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -5472,7 +6276,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Meesho)</t>
+          <t>Software Engineer / AI Systems (Microsoft India)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5502,12 +6306,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -5539,7 +6343,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Paytm)</t>
+          <t>Software Engineer / AI Systems (Atlassian)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5569,12 +6373,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -5606,7 +6410,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (AMD India)</t>
+          <t>Software Engineer / AI Systems (Postman)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5636,12 +6440,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 16, 2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -5668,12 +6472,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Devolity</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Software Engineer / AI Systems (Krutrim AI)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5683,32 +6487,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 16, 2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -5728,7 +6532,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/sr-azure-cloud-engineer-at-devolity-4404850484?position=4&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=IgK6vAIKucjrQJ0LLni7ew%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -5740,7 +6544,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Groww)</t>
+          <t>Software Engineer / AI Systems (Amazon India)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5770,12 +6574,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 16, 2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -5807,7 +6611,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (PhonePe)</t>
+          <t>Software Engineer / AI Systems (Salesforce India)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5837,12 +6641,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 16, 2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5874,7 +6678,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Adobe India)</t>
+          <t>Software Engineer / AI Systems (Sarvam AI)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5904,12 +6708,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 15, 2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5941,7 +6745,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (InMobi)</t>
+          <t>Software Engineer / AI Systems (Pine Labs)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5971,12 +6775,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Aug 11, 2026</t>
+          <t>Aug 15, 2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -6008,7 +6812,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Uber India)</t>
+          <t>Software Engineer / AI Systems (NVIDIA India)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6038,12 +6842,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Aug 11, 2026</t>
+          <t>Aug 15, 2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -6070,12 +6874,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Software Engineer, Developer Experience</t>
+          <t>Software Engineer / AI Systems (Oracle India)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6085,32 +6889,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Aug 11, 2026</t>
+          <t>Aug 15, 2026</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -6130,19 +6934,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/49bdf081-6e20-4323-8c73-6d6b19544ff5/application</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Accenture in India</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Custom Software Engineer</t>
+          <t>Software Engineer / AI Systems (CRED)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6152,37 +6956,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Aug 08, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6197,7 +7001,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4454591390?position=1&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=ArzemHDxFnemBL291umnmA%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -6209,7 +7013,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Flipkart)</t>
+          <t>Software Engineer / AI Systems (Zerodha)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6239,17 +7043,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Aug 08, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -6271,12 +7075,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Accenture in India</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Custom Software Engineer</t>
+          <t>Software Engineer / AI Systems (Intel India)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6286,37 +7090,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nagpur, Maharashtra, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Aug 07, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -6331,7 +7135,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/custom-software-engineer-at-accenture-in-india-4448374964?position=2&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=Sblf5B5GG59xm%2B4C4TwKYA%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -6343,7 +7147,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Swiggy)</t>
+          <t>Software Engineer / AI Systems (Cisco India)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6373,17 +7177,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Aug 07, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6405,12 +7209,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>YouthNet</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Software Developer Job Vacancy in Kohima Nagaland</t>
+          <t>Software Engineer / AI Systems (Meesho)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6420,37 +7224,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kohima, Nagaland, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Aug 06, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6465,7 +7269,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-developer-job-vacancy-in-kohima-nagaland-at-youthnet-4247411794?position=3&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=PBEN9oTHtxysOxLG1e45OQ%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -6477,7 +7281,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Zomato)</t>
+          <t>Software Engineer / AI Systems (Paytm)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6507,17 +7311,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Aug 06, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>🟡 AGING</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6539,12 +7343,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ServLogic Innovations LLP.</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Software Engineer / AI Systems (AMD India)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6554,37 +7358,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Port Blair, Andaman and Nicobar Islands, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Jul 28, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -6599,7 +7403,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/senior-net-developer-at-servlogic-innovations-llp-4446990115?position=5&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=S102FtHUL%2B4XfY8vleUNcg%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -6611,7 +7415,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Samsung R&amp;D India)</t>
+          <t>Software Engineer / AI Systems (Groww)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6641,17 +7445,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Jul 28, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -6673,12 +7477,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marduk Technologies</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer / AI Systems (PhonePe)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6688,37 +7492,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pocket 6 Sector 21, Delhi, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -6733,7 +7537,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-developer-at-marduk-technologies-4449817611?position=6&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=8BSgfiq%2FVRdXcAHEzm9Ryg%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -6745,7 +7549,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (LG Electronics R&amp;D)</t>
+          <t>Software Engineer / AI Systems (Adobe India)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6775,17 +7579,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -6807,12 +7611,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NeonScouts</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Priya Sharma</t>
+          <t>Software Engineer / AI Systems (InMobi)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6822,37 +7626,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Anupgarh, Rajasthan, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Jul 26, 2026</t>
+          <t>Aug 11, 2026</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6867,7 +7671,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/priya-sharma-at-neonscouts-4445853567?position=7&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=A8A%2BuAJnlWwObh5Bm0Rgmw%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -6879,7 +7683,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Nokia India)</t>
+          <t>Software Engineer / AI Systems (Uber India)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6909,17 +7713,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Jul 26, 2026</t>
+          <t>Aug 11, 2026</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>🟠 STALE</t>
+          <t>🟢 FRESH</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6941,12 +7745,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Software Developer 3</t>
+          <t>Software Engineer / AI Systems (Flipkart)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6956,37 +7760,37 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0-2 yrs</t>
+          <t>1-3 yrs</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trivandrum, Kerala, India</t>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Competitive (Market Standard)</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Jul 04, 2026</t>
+          <t>Aug 08, 2026</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>44d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>🔴 VERY STALE</t>
+          <t>🟡 AGING</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -7001,7 +7805,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-developer-3-at-oracle-4438722956?position=8&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=NZcvnFuRB8m2i2DcD%2FcYNQ%3D%3D</t>
+          <t>#</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7817,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Software Engineer / AI Systems (Google India)</t>
+          <t>Software Engineer / AI Systems (Swiggy)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7043,17 +7847,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Jul 04, 2026</t>
+          <t>Aug 07, 2026</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>44d</t>
+          <t>10d</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>🔴 VERY STALE</t>
+          <t>🟡 AGING</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -7075,67 +7879,871 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (Zomato)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Aug 06, 2026</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>11d</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>🟡 AGING</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (Samsung R&amp;D India)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Jul 28, 2026</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20d</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>🟠 STALE</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (LG Electronics R&amp;D)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Jul 27, 2026</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>21d</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>🟠 STALE</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (Nokia India)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Jul 26, 2026</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>22d</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>🟠 STALE</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Software Engineer / AI Systems (Google India)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1-3 yrs</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>India (Bangalore / Gurgaon / Remote)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Jul 04, 2026</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>44d</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>🔴 VERY STALE</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Soft Solutions</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Greater Lucknow Area</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Aug 16, 2026</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>🟢 FRESH</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/software-developer-at-soft-solutions-4306120377?position=10&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=O9loeVXlEh8YatYRtS416Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Clearwater Analytics</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Mumbai Metropolitan Region</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Aug 15, 2026</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>🟢 FRESH</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/software-development-engineer-at-clearwater-analytics-4450330786?position=1&amp;pageNum=1&amp;refId=u61WPYQrHvSOHNn5R%2BiqiA%3D%3D&amp;trackingId=gcJQ%2BFhcq5cziu%2BUR1CObA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Fullscreens</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineers</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Greater Kolkata Area</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3d</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>🟢 FRESH</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-engineers-at-fullscreens-4448951607?position=2&amp;pageNum=1&amp;refId=u61WPYQrHvSOHNn5R%2BiqiA%3D%3D&amp;trackingId=obhzqIBnMqveUruzIWMesQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Xerox</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SOFTWARE ENGINEER 3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Greater Kolkata Area</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>⚪ UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-3-at-xerox-4362193461?position=1&amp;pageNum=1&amp;refId=un0n5dcspQ2AFk%2FvdLjKiA%3D%3D&amp;trackingId=F%2FvlHHSkgq0fsvWnMMYFEQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Devolity</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Sr. Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Delhi, Delhi, India</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4d</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>🟢 FRESH</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/sr-azure-cloud-engineer-at-devolity-4404850484?position=4&amp;pageNum=0&amp;refId=1IG6eUwkRGmNGK8KklZsCQ%3D%3D&amp;trackingId=IgK6vAIKucjrQJ0LLni7ew%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Software Engineer, Infrastructure </t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Software Engineer, Developer Experience</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>0-2 yrs</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Hyderabad, India</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Competitive (Market Standard)</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>🟢 FRESH</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/notion/49bdf081-6e20-4323-8c73-6d6b19544ff5/application</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>WebEngage</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>Recent</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>⚪ UNKNOWN</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>CONFIRMED_POSTED</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>❌ NO</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/notion/42f18ccd-c4c8-4a85-8c1f-de12c575fe87/application</t>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-java-at-webengage-4261040176?position=1&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=%2FZU90nGJGeudtfryQPTBSw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Charles Schwab India</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Software Developer (Java)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0-2 yrs</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Competitive (Market Standard)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>⚪ UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>CONFIRMED_POSTED</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/software-developer-java-at-charles-schwab-india-4443274661?position=2&amp;pageNum=0&amp;refId=IdKDnnurVvgKyXjtSu9LAg%3D%3D&amp;trackingId=swSmGS3lpWeK7fsyDX5OPg%3D%3D</t>
         </is>
       </c>
     </row>
